--- a/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E250798E-E874-43D0-8B69-FA43772E6253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D0DE081-1949-4CF0-B38E-6F4866006899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="19.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="185">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -447,6 +447,229 @@
   </si>
   <si>
     <t xml:space="preserve">IGOR MENDES FORTINI MUNHOZ                   </t>
+  </si>
+  <si>
+    <t>20/01/2026</t>
+  </si>
+  <si>
+    <t>PANDABATERA LTDA ME CNPJ 55228814000170</t>
+  </si>
+  <si>
+    <t>Dados bancários inválidos</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>Maria Da Conceicao Costa Ferreira Nunes CPF 14700204320</t>
+  </si>
+  <si>
+    <t>Não consta LIMBO - Há proposta transmitida via Auto Compara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA LORO SPONCHIADO                       </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6 através desse e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F G SANTOS LTDA ME                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *PRAZO EXPIRADO * repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Kit Gás, Chassi, Frente e lateral do motorista, Veículo Blindado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGNALDO LOPES TAVARES                        </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro e motorista, Traseira e lateral do motorista e passageiro (Não enquadrada corretamente), Painel com carro ligado (Veiculo desligado), Chassi (local incorreto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASTRO E ALVES LTDA ME                       </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Documento do veículo, Chassi // VEÍCULO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINHEIRO SERVICE LTDA ME                     </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Frente e lateral do passageiro, Ta e lateral do motorista, Painel , Chassi, T e lateral do pas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISMENIA MARIA DE SOUZA MARTINS               </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI (LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANO MATTOS DE SOUZA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS // PORTA MALAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANGELA MARIA CORREA                       </t>
+  </si>
+  <si>
+    <t>Proposta transmitida como não sendo vigência anual(16/01/2025 à 14
+/01/2026), sistema não permite, estamos nesta data efetuando a rec
+usa dessa, para que possam transmitir um novo processo com vigênci
+aanual 16/01/2025 à 16/01/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO PAULINO DE OLIVEIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: PORTA MALAS VAZIO. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALTER CAPINAM MACEDO FILHO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: Fren e lateral do passageiro e motorista, Tras e lateral do passageiro e motorista enquad a plca, Motor e placa. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANE SOARES DA SILVA                      </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Frente e lateral do passageiro, Chassi, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMUNDO NONATO GALVAO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEX SALVIATI                                </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: FRENTE LAT. DIR.E ESQ. TRASEIRA LAT. DIR. E ESQ. (FOTO EMBAÇADA) CHASSI (LOCAL INCORRETO) DOCUMENTO (FOTO EMBAÇADA) HODOMETRO (DESLIGADO) MOTOR (FOTO EMBAÇADA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAURI FERREIRA ATANASIO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA VALDINEIDE DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA APARECIDA ROSSONI ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA APARECIDA GOMES NEVES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO MANOEL DA SILVA                    </t>
+  </si>
+  <si>
+    <t>Pendência do envio da declaração de origem de recursos PEP - Pessoas Politicamente Expostas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCENIO TORRES GALINDO FILHO                 </t>
+  </si>
+  <si>
+    <t>Veiculo em duplicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AYLTON LEVANDOSQUI RODRIGUES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYLENA SOARES DE OLIVEIRA VIANA              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CAROLINA DOS SANTOS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cópia da apólice congênere c
+om vigência de 2026 a 2027.
+– Endosso de cancelamento emitido.&lt;
+br&gt;.........</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEVERINO EVARISTO ALVES                      </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2025/2026 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIAGO FERREIRA DE LIMA                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não h
+á possibilidade efetuar a transferência de bônus para o(a) senhor(
+a) TIAGO FERREIRA DE LIMA, pois este não consta como condutor na a
+pólice anterior.
+Neste caso, iremos realizar a recusa desta p
+roposta, para conclusão do processo é necessário informar o e-mail
+do segurado anterior ALESSANDRA DOS SANTOS GONCALVES SILVA, para
+que o mesmo também fique ciente da recusa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIZANDRA ANDRADE DE OLIVEIRA                 </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGDA PONTIN VIGANO                          </t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas houve quebra de vigência de 3
+65 dias, portanto devem-se excluir todas as classes de bônus e con
+siderar como seguro novo.
+Com a correção ficou 10x R$ 345,86.
+Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEVI LIMA GRETER                             </t>
+  </si>
+  <si>
+    <t>Proposta transmitida como vigência não sendo anual 22/01/2026 à 14
+/01/2027, sistema não permite prosseguir com a emissão, estamos ne
+sta data efetuando a recusa da mesma para que possam transmitir co
+mvigência correta anual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELYSEU PELLENZ                               </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+– Cópia da apólice congênere c
+om vigência de 2026 a 2027;
+– Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABRICIO COLARES BARBOSA FILHO               </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há possibilidade
+efetuar a transferência de bônus para o(a) senhor(a) FABRICIO COLARES BARBOSA
+FILHO, pois este não consta como condutor na apólice anterior.
+Neste caso, iremos realizar a recusa desta proposta, para conclusão do processo
+é necessário informar o emaildo segurado anterior (VALERIA FREITAS SAMPAIO
+COLARES), para que o mesmo também fique ciente da recusa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDGARD TEIXEIRA DE MELLO NETO                </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL NETO DA SILVA                         </t>
   </si>
 </sst>
 </file>
@@ -511,7 +734,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -732,12 +955,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -922,37 +1156,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1362,7 +1584,7 @@
       <c r="C3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="74" t="s">
+      <c r="D3" s="73" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="64">
@@ -1391,19 +1613,19 @@
       <c r="C4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="22">
         <v>136105116</v>
       </c>
       <c r="E4" s="17">
         <v>3450205946</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="77" t="s">
+      <c r="H4" s="45" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="44">
@@ -1420,16 +1642,16 @@
       <c r="C5" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="22">
         <v>136162103</v>
       </c>
       <c r="E5" s="17">
         <v>3450210841</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="72" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="45" t="s">
@@ -1449,16 +1671,16 @@
       <c r="C6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="22">
         <v>136162072</v>
       </c>
       <c r="E6" s="17">
         <v>3450210820</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="73" t="s">
+      <c r="G6" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="45" t="s">
@@ -1478,16 +1700,16 @@
       <c r="C7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="22">
         <v>136167809</v>
       </c>
       <c r="E7" s="17">
         <v>3450211402</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="45" t="s">
@@ -1507,16 +1729,16 @@
       <c r="C8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="22">
         <v>136166035</v>
       </c>
       <c r="E8" s="17">
         <v>3450211248</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="72" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="45" t="s">
@@ -1536,16 +1758,16 @@
       <c r="C9" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="22">
         <v>136174298</v>
       </c>
       <c r="E9" s="17">
         <v>3450211853</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="73" t="s">
+      <c r="G9" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="45" t="s">
@@ -1565,16 +1787,16 @@
       <c r="C10" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="22">
         <v>136175680</v>
       </c>
       <c r="E10" s="17">
         <v>3450211985</v>
       </c>
-      <c r="F10" s="72" t="s">
+      <c r="F10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="45" t="s">
@@ -1594,16 +1816,16 @@
       <c r="C11" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="22">
         <v>136164243</v>
       </c>
       <c r="E11" s="17">
         <v>3450211072</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -1623,16 +1845,16 @@
       <c r="C12" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="22">
         <v>136198766</v>
       </c>
       <c r="E12" s="17">
         <v>3450211941</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H12" s="45" t="s">
@@ -1652,16 +1874,16 @@
       <c r="C13" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="22">
         <v>136201029</v>
       </c>
       <c r="E13" s="17">
         <v>3450214174</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="73" t="s">
+      <c r="G13" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="45" t="s">
@@ -1681,16 +1903,16 @@
       <c r="C14" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="22">
         <v>136161353</v>
       </c>
       <c r="E14" s="17">
         <v>3450210698</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="45" t="s">
@@ -1710,16 +1932,16 @@
       <c r="C15" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="22">
         <v>136209773</v>
       </c>
       <c r="E15" s="17">
         <v>3450214944</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="73" t="s">
+      <c r="G15" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H15" s="45" t="s">
@@ -1739,16 +1961,16 @@
       <c r="C16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="22">
         <v>136203437</v>
       </c>
       <c r="E16" s="17">
         <v>3450214372</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="F16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H16" s="45" t="s">
@@ -1768,16 +1990,16 @@
       <c r="C17" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="22">
         <v>136209760</v>
       </c>
       <c r="E17" s="17">
         <v>3450214933</v>
       </c>
-      <c r="F17" s="72" t="s">
+      <c r="F17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="73" t="s">
+      <c r="G17" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H17" s="45" t="s">
@@ -1797,16 +2019,16 @@
       <c r="C18" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="22">
         <v>136227274</v>
       </c>
       <c r="E18" s="17">
         <v>3450216320</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="73" t="s">
+      <c r="G18" s="72" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="45" t="s">
@@ -1826,16 +2048,16 @@
       <c r="C19" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="22">
         <v>136220573</v>
       </c>
       <c r="E19" s="17">
         <v>3450215681</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="73" t="s">
+      <c r="G19" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H19" s="45" t="s">
@@ -1855,16 +2077,16 @@
       <c r="C20" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="22">
         <v>136216117</v>
       </c>
       <c r="E20" s="17">
         <v>3450215362</v>
       </c>
-      <c r="F20" s="72" t="s">
+      <c r="F20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H20" s="45" t="s">
@@ -1884,16 +2106,16 @@
       <c r="C21" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="75">
+      <c r="D21" s="22">
         <v>136196673</v>
       </c>
       <c r="E21" s="17">
         <v>3450213811</v>
       </c>
-      <c r="F21" s="72" t="s">
+      <c r="F21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="73" t="s">
+      <c r="G21" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="45" t="s">
@@ -1913,16 +2135,16 @@
       <c r="C22" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="22">
         <v>136227805</v>
       </c>
       <c r="E22" s="17">
         <v>3450216374</v>
       </c>
-      <c r="F22" s="72" t="s">
+      <c r="F22" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="73" t="s">
+      <c r="G22" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H22" s="45" t="s">
@@ -1942,16 +2164,16 @@
       <c r="C23" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="75">
+      <c r="D23" s="22">
         <v>136239888</v>
       </c>
       <c r="E23" s="17">
         <v>3450217067</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="73" t="s">
+      <c r="G23" s="72" t="s">
         <v>47</v>
       </c>
       <c r="H23" s="45" t="s">
@@ -1971,16 +2193,16 @@
       <c r="C24" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D24" s="22">
         <v>136220049</v>
       </c>
       <c r="E24" s="17">
         <v>3450215637</v>
       </c>
-      <c r="F24" s="72" t="s">
+      <c r="F24" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="73" t="s">
+      <c r="G24" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H24" s="45" t="s">
@@ -2000,16 +2222,16 @@
       <c r="C25" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="75">
+      <c r="D25" s="22">
         <v>136264765</v>
       </c>
       <c r="E25" s="17">
         <v>3450219146</v>
       </c>
-      <c r="F25" s="72" t="s">
+      <c r="F25" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="73" t="s">
+      <c r="G25" s="72" t="s">
         <v>47</v>
       </c>
       <c r="H25" s="45" t="s">
@@ -2029,16 +2251,16 @@
       <c r="C26" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="75">
+      <c r="D26" s="22">
         <v>136266207</v>
       </c>
       <c r="E26" s="17">
         <v>3450219234</v>
       </c>
-      <c r="F26" s="72" t="s">
+      <c r="F26" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="73" t="s">
+      <c r="G26" s="72" t="s">
         <v>47</v>
       </c>
       <c r="H26" s="45" t="s">
@@ -2058,16 +2280,16 @@
       <c r="C27" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="75">
+      <c r="D27" s="22">
         <v>136181906</v>
       </c>
       <c r="E27" s="17">
         <v>3450212722</v>
       </c>
-      <c r="F27" s="72" t="s">
+      <c r="F27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="73" t="s">
+      <c r="G27" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H27" s="45" t="s">
@@ -2087,19 +2309,19 @@
       <c r="C28" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="75">
+      <c r="D28" s="22">
         <v>136126331</v>
       </c>
       <c r="E28" s="17">
         <v>3450207816</v>
       </c>
-      <c r="F28" s="72" t="s">
+      <c r="F28" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="73" t="s">
+      <c r="G28" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="77" t="s">
+      <c r="H28" s="45" t="s">
         <v>63</v>
       </c>
       <c r="I28" s="44">
@@ -2116,16 +2338,16 @@
       <c r="C29" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="75">
+      <c r="D29" s="22">
         <v>136203766</v>
       </c>
       <c r="E29" s="17">
         <v>3450214405</v>
       </c>
-      <c r="F29" s="72" t="s">
+      <c r="F29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="73" t="s">
+      <c r="G29" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H29" s="45" t="s">
@@ -2145,16 +2367,16 @@
       <c r="C30" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="75">
+      <c r="D30" s="22">
         <v>136284827</v>
       </c>
       <c r="E30" s="17">
         <v>3450220598</v>
       </c>
-      <c r="F30" s="72" t="s">
+      <c r="F30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="72" t="s">
         <v>47</v>
       </c>
       <c r="H30" s="45" t="s">
@@ -2174,16 +2396,16 @@
       <c r="C31" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="75">
+      <c r="D31" s="22">
         <v>136238433</v>
       </c>
       <c r="E31" s="17">
         <v>3450216980</v>
       </c>
-      <c r="F31" s="72" t="s">
+      <c r="F31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="73" t="s">
+      <c r="G31" s="72" t="s">
         <v>47</v>
       </c>
       <c r="H31" s="45" t="s">
@@ -2203,19 +2425,19 @@
       <c r="C32" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="75">
+      <c r="D32" s="22">
         <v>136115118</v>
       </c>
       <c r="E32" s="17">
         <v>3450206419</v>
       </c>
-      <c r="F32" s="72" t="s">
+      <c r="F32" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G32" s="73" t="s">
+      <c r="G32" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="H32" s="77" t="s">
+      <c r="H32" s="45" t="s">
         <v>70</v>
       </c>
       <c r="I32" s="44">
@@ -2232,16 +2454,16 @@
       <c r="C33" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="75">
+      <c r="D33" s="22">
         <v>136220894</v>
       </c>
       <c r="E33" s="17">
         <v>3450215736</v>
       </c>
-      <c r="F33" s="72" t="s">
+      <c r="F33" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="73" t="s">
+      <c r="G33" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H33" s="45" t="s">
@@ -2261,16 +2483,16 @@
       <c r="C34" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="75">
+      <c r="D34" s="22">
         <v>136216946</v>
       </c>
       <c r="E34" s="17">
         <v>3450214240</v>
       </c>
-      <c r="F34" s="72" t="s">
+      <c r="F34" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="73" t="s">
+      <c r="G34" s="72" t="s">
         <v>13</v>
       </c>
       <c r="H34" s="45" t="s">
@@ -2290,16 +2512,16 @@
       <c r="C35" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="75">
+      <c r="D35" s="22">
         <v>136209535</v>
       </c>
       <c r="E35" s="17">
         <v>3450214911</v>
       </c>
-      <c r="F35" s="72" t="s">
+      <c r="F35" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G35" s="73" t="s">
+      <c r="G35" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H35" s="45" t="s">
@@ -2319,16 +2541,16 @@
       <c r="C36" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="75">
+      <c r="D36" s="22">
         <v>136229601</v>
       </c>
       <c r="E36" s="17">
         <v>3450216561</v>
       </c>
-      <c r="F36" s="72" t="s">
+      <c r="F36" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="73" t="s">
+      <c r="G36" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H36" s="45" t="s">
@@ -2348,16 +2570,16 @@
       <c r="C37" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="75">
+      <c r="D37" s="22">
         <v>136121181</v>
       </c>
       <c r="E37" s="17">
         <v>3450207090</v>
       </c>
-      <c r="F37" s="72" t="s">
+      <c r="F37" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="73" t="s">
+      <c r="G37" s="72" t="s">
         <v>13</v>
       </c>
       <c r="H37" s="45" t="s">
@@ -2377,19 +2599,19 @@
       <c r="C38" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="75">
+      <c r="D38" s="22">
         <v>136117926</v>
       </c>
       <c r="E38" s="17">
         <v>3450206727</v>
       </c>
-      <c r="F38" s="72" t="s">
+      <c r="F38" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="73" t="s">
+      <c r="G38" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="77" t="s">
+      <c r="H38" s="45" t="s">
         <v>80</v>
       </c>
       <c r="I38" s="44">
@@ -2406,19 +2628,19 @@
       <c r="C39" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="75">
+      <c r="D39" s="22">
         <v>136120139</v>
       </c>
       <c r="E39" s="17">
         <v>3450206958</v>
       </c>
-      <c r="F39" s="72" t="s">
+      <c r="F39" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G39" s="73" t="s">
+      <c r="G39" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="77" t="s">
+      <c r="H39" s="45" t="s">
         <v>82</v>
       </c>
       <c r="I39" s="44">
@@ -2435,19 +2657,19 @@
       <c r="C40" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="75">
+      <c r="D40" s="22">
         <v>136121993</v>
       </c>
       <c r="E40" s="17">
         <v>3450207156</v>
       </c>
-      <c r="F40" s="72" t="s">
+      <c r="F40" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G40" s="73" t="s">
+      <c r="G40" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H40" s="77" t="s">
+      <c r="H40" s="45" t="s">
         <v>84</v>
       </c>
       <c r="I40" s="44">
@@ -2464,19 +2686,19 @@
       <c r="C41" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="75">
+      <c r="D41" s="22">
         <v>136219683</v>
       </c>
       <c r="E41" s="22">
         <v>3450215582</v>
       </c>
-      <c r="F41" s="72" t="s">
+      <c r="F41" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="73" t="s">
+      <c r="G41" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="77" t="s">
+      <c r="H41" s="45" t="s">
         <v>86</v>
       </c>
       <c r="I41" s="44">
@@ -2493,19 +2715,19 @@
       <c r="C42" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="75">
+      <c r="D42" s="22">
         <v>136124148</v>
       </c>
       <c r="E42" s="22">
         <v>3450207453</v>
       </c>
-      <c r="F42" s="72" t="s">
+      <c r="F42" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G42" s="73" t="s">
+      <c r="G42" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="77" t="s">
+      <c r="H42" s="45" t="s">
         <v>88</v>
       </c>
       <c r="I42" s="44">
@@ -2522,19 +2744,19 @@
       <c r="C43" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="75">
+      <c r="D43" s="22">
         <v>136127037</v>
       </c>
       <c r="E43" s="22">
         <v>3450207926</v>
       </c>
-      <c r="F43" s="72" t="s">
+      <c r="F43" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G43" s="73" t="s">
+      <c r="G43" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H43" s="77" t="s">
+      <c r="H43" s="45" t="s">
         <v>90</v>
       </c>
       <c r="I43" s="44">
@@ -2551,19 +2773,19 @@
       <c r="C44" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="75">
+      <c r="D44" s="22">
         <v>136225063</v>
       </c>
       <c r="E44" s="22">
         <v>3450216143</v>
       </c>
-      <c r="F44" s="72" t="s">
+      <c r="F44" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="73" t="s">
+      <c r="G44" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="77" t="s">
+      <c r="H44" s="45" t="s">
         <v>92</v>
       </c>
       <c r="I44" s="44">
@@ -2580,19 +2802,19 @@
       <c r="C45" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="75">
+      <c r="D45" s="22">
         <v>136130942</v>
       </c>
       <c r="E45" s="22">
         <v>3450208212</v>
       </c>
-      <c r="F45" s="72" t="s">
+      <c r="F45" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G45" s="73" t="s">
+      <c r="G45" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="77" t="s">
+      <c r="H45" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I45" s="44">
@@ -2609,19 +2831,19 @@
       <c r="C46" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="75">
+      <c r="D46" s="22">
         <v>136131146</v>
       </c>
       <c r="E46" s="22">
         <v>3450206530</v>
       </c>
-      <c r="F46" s="72" t="s">
+      <c r="F46" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G46" s="73" t="s">
+      <c r="G46" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="77" t="s">
+      <c r="H46" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I46" s="44">
@@ -2638,19 +2860,19 @@
       <c r="C47" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="75">
+      <c r="D47" s="22">
         <v>136132033</v>
       </c>
       <c r="E47" s="22">
         <v>3450208290</v>
       </c>
-      <c r="F47" s="72" t="s">
+      <c r="F47" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G47" s="73" t="s">
+      <c r="G47" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H47" s="77" t="s">
+      <c r="H47" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I47" s="44">
@@ -2667,19 +2889,19 @@
       <c r="C48" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="75">
+      <c r="D48" s="22">
         <v>136133116</v>
       </c>
       <c r="E48" s="22">
         <v>3450208333</v>
       </c>
-      <c r="F48" s="72" t="s">
+      <c r="F48" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G48" s="73" t="s">
+      <c r="G48" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H48" s="77" t="s">
+      <c r="H48" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I48" s="44">
@@ -2696,19 +2918,19 @@
       <c r="C49" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="75">
+      <c r="D49" s="22">
         <v>136134361</v>
       </c>
       <c r="E49" s="22">
         <v>3450195793</v>
       </c>
-      <c r="F49" s="72" t="s">
+      <c r="F49" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="73" t="s">
+      <c r="G49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H49" s="77" t="s">
+      <c r="H49" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I49" s="44">
@@ -2725,19 +2947,19 @@
       <c r="C50" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D50" s="75">
+      <c r="D50" s="22">
         <v>136137429</v>
       </c>
       <c r="E50" s="22">
         <v>3450208861</v>
       </c>
-      <c r="F50" s="72" t="s">
+      <c r="F50" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G50" s="73" t="s">
+      <c r="G50" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H50" s="77" t="s">
+      <c r="H50" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I50" s="44">
@@ -2754,19 +2976,19 @@
       <c r="C51" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="75">
+      <c r="D51" s="22">
         <v>136137680</v>
       </c>
       <c r="E51" s="22">
         <v>3450208993</v>
       </c>
-      <c r="F51" s="72" t="s">
+      <c r="F51" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G51" s="73" t="s">
+      <c r="G51" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H51" s="77" t="s">
+      <c r="H51" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I51" s="44">
@@ -2783,19 +3005,19 @@
       <c r="C52" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="75">
+      <c r="D52" s="22">
         <v>136140242</v>
       </c>
       <c r="E52" s="22">
         <v>3450209280</v>
       </c>
-      <c r="F52" s="72" t="s">
+      <c r="F52" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G52" s="73" t="s">
+      <c r="G52" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="H52" s="77" t="s">
+      <c r="H52" s="45" t="s">
         <v>100</v>
       </c>
       <c r="I52" s="44">
@@ -2812,19 +3034,19 @@
       <c r="C53" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="75">
+      <c r="D53" s="22">
         <v>136150239</v>
       </c>
       <c r="E53" s="22">
         <v>3450200182</v>
       </c>
-      <c r="F53" s="72" t="s">
+      <c r="F53" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G53" s="73" t="s">
+      <c r="G53" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="77" t="s">
+      <c r="H53" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I53" s="44">
@@ -2841,19 +3063,19 @@
       <c r="C54" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="75">
+      <c r="D54" s="22">
         <v>136153470</v>
       </c>
       <c r="E54" s="22">
         <v>3450208784</v>
       </c>
-      <c r="F54" s="72" t="s">
+      <c r="F54" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="73" t="s">
+      <c r="G54" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H54" s="77" t="s">
+      <c r="H54" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I54" s="44">
@@ -2870,19 +3092,19 @@
       <c r="C55" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="75">
+      <c r="D55" s="22">
         <v>136155363</v>
       </c>
       <c r="E55" s="22">
         <v>3450209312</v>
       </c>
-      <c r="F55" s="72" t="s">
+      <c r="F55" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G55" s="73" t="s">
+      <c r="G55" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H55" s="77" t="s">
+      <c r="H55" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I55" s="44">
@@ -2899,19 +3121,19 @@
       <c r="C56" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="75">
+      <c r="D56" s="22">
         <v>136158177</v>
       </c>
       <c r="E56" s="22">
         <v>3450210478</v>
       </c>
-      <c r="F56" s="72" t="s">
+      <c r="F56" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G56" s="73" t="s">
+      <c r="G56" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H56" s="77" t="s">
+      <c r="H56" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I56" s="44">
@@ -2928,19 +3150,19 @@
       <c r="C57" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="75">
+      <c r="D57" s="22">
         <v>136159061</v>
       </c>
       <c r="E57" s="22">
         <v>3450210522</v>
       </c>
-      <c r="F57" s="72" t="s">
+      <c r="F57" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G57" s="73" t="s">
+      <c r="G57" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H57" s="77" t="s">
+      <c r="H57" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I57" s="44">
@@ -2957,19 +3179,19 @@
       <c r="C58" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="75">
+      <c r="D58" s="22">
         <v>136159572</v>
       </c>
       <c r="E58" s="22">
         <v>3450210555</v>
       </c>
-      <c r="F58" s="72" t="s">
+      <c r="F58" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="73" t="s">
+      <c r="G58" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H58" s="77" t="s">
+      <c r="H58" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I58" s="44">
@@ -2986,19 +3208,19 @@
       <c r="C59" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="75">
+      <c r="D59" s="22">
         <v>136160934</v>
       </c>
       <c r="E59" s="22">
         <v>3450210621</v>
       </c>
-      <c r="F59" s="72" t="s">
+      <c r="F59" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G59" s="73" t="s">
+      <c r="G59" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="H59" s="77" t="s">
+      <c r="H59" s="45" t="s">
         <v>27</v>
       </c>
       <c r="I59" s="44">
@@ -3015,19 +3237,19 @@
       <c r="C60" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="75">
+      <c r="D60" s="22">
         <v>136161602</v>
       </c>
       <c r="E60" s="22">
         <v>3450210731</v>
       </c>
-      <c r="F60" s="72" t="s">
+      <c r="F60" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G60" s="76" t="s">
+      <c r="G60" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="H60" s="77" t="s">
+      <c r="H60" s="45" t="s">
         <v>26</v>
       </c>
       <c r="I60" s="44">
@@ -3044,16 +3266,16 @@
       <c r="C61" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="75">
+      <c r="D61" s="22">
         <v>136163135</v>
       </c>
       <c r="E61" s="22">
         <v>3450210973</v>
       </c>
-      <c r="F61" s="72" t="s">
+      <c r="F61" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G61" s="73" t="s">
+      <c r="G61" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="45" t="s">
@@ -3073,16 +3295,16 @@
       <c r="C62" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D62" s="75">
+      <c r="D62" s="22">
         <v>136166168</v>
       </c>
       <c r="E62" s="17">
         <v>3450211260</v>
       </c>
-      <c r="F62" s="72" t="s">
+      <c r="F62" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="73" t="s">
+      <c r="G62" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H62" s="45" t="s">
@@ -3102,16 +3324,16 @@
       <c r="C63" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="75">
+      <c r="D63" s="22">
         <v>136167576</v>
       </c>
       <c r="E63" s="17">
         <v>3450211370</v>
       </c>
-      <c r="F63" s="72" t="s">
+      <c r="F63" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G63" s="73" t="s">
+      <c r="G63" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H63" s="45" t="s">
@@ -3131,16 +3353,16 @@
       <c r="C64" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D64" s="75">
+      <c r="D64" s="22">
         <v>136170190</v>
       </c>
       <c r="E64" s="17">
         <v>3450211480</v>
       </c>
-      <c r="F64" s="72" t="s">
+      <c r="F64" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G64" s="73" t="s">
+      <c r="G64" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H64" s="45" t="s">
@@ -3160,16 +3382,16 @@
       <c r="C65" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="75">
+      <c r="D65" s="22">
         <v>136173186</v>
       </c>
       <c r="E65" s="17">
         <v>3450210797</v>
       </c>
-      <c r="F65" s="72" t="s">
+      <c r="F65" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G65" s="73" t="s">
+      <c r="G65" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H65" s="45" t="s">
@@ -3189,16 +3411,16 @@
       <c r="C66" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="75">
+      <c r="D66" s="22">
         <v>136177988</v>
       </c>
       <c r="E66" s="17">
         <v>3450212282</v>
       </c>
-      <c r="F66" s="72" t="s">
+      <c r="F66" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G66" s="73" t="s">
+      <c r="G66" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H66" s="12" t="s">
@@ -3218,16 +3440,16 @@
       <c r="C67" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="75">
+      <c r="D67" s="22">
         <v>136178449</v>
       </c>
       <c r="E67" s="17">
         <v>3450212337</v>
       </c>
-      <c r="F67" s="72" t="s">
+      <c r="F67" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G67" s="73" t="s">
+      <c r="G67" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H67" s="12" t="s">
@@ -3247,16 +3469,16 @@
       <c r="C68" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D68" s="75">
+      <c r="D68" s="22">
         <v>136178689</v>
       </c>
       <c r="E68" s="17">
         <v>3450212370</v>
       </c>
-      <c r="F68" s="72" t="s">
+      <c r="F68" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G68" s="73" t="s">
+      <c r="G68" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H68" s="12" t="s">
@@ -3276,16 +3498,16 @@
       <c r="C69" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="75">
+      <c r="D69" s="22">
         <v>136181166</v>
       </c>
       <c r="E69" s="17">
         <v>3450212634</v>
       </c>
-      <c r="F69" s="72" t="s">
+      <c r="F69" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G69" s="73" t="s">
+      <c r="G69" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H69" s="12" t="s">
@@ -3305,16 +3527,16 @@
       <c r="C70" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="75">
+      <c r="D70" s="22">
         <v>136186468</v>
       </c>
       <c r="E70" s="17">
         <v>3450213151</v>
       </c>
-      <c r="F70" s="72" t="s">
+      <c r="F70" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G70" s="73" t="s">
+      <c r="G70" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="12" t="s">
@@ -3334,16 +3556,16 @@
       <c r="C71" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D71" s="75">
+      <c r="D71" s="22">
         <v>136187002</v>
       </c>
       <c r="E71" s="17">
         <v>3450213228</v>
       </c>
-      <c r="F71" s="72" t="s">
+      <c r="F71" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G71" s="73" t="s">
+      <c r="G71" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H71" s="12" t="s">
@@ -3363,16 +3585,16 @@
       <c r="C72" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="75">
+      <c r="D72" s="22">
         <v>136189995</v>
       </c>
       <c r="E72" s="17">
         <v>3450213514</v>
       </c>
-      <c r="F72" s="72" t="s">
+      <c r="F72" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G72" s="73" t="s">
+      <c r="G72" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H72" s="12" t="s">
@@ -3392,16 +3614,16 @@
       <c r="C73" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D73" s="75">
+      <c r="D73" s="22">
         <v>136190185</v>
       </c>
       <c r="E73" s="17">
         <v>3450213525</v>
       </c>
-      <c r="F73" s="72" t="s">
+      <c r="F73" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G73" s="73" t="s">
+      <c r="G73" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H73" s="12" t="s">
@@ -3421,16 +3643,16 @@
       <c r="C74" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="75">
+      <c r="D74" s="22">
         <v>136191230</v>
       </c>
       <c r="E74" s="17">
         <v>3450213624</v>
       </c>
-      <c r="F74" s="72" t="s">
+      <c r="F74" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G74" s="73" t="s">
+      <c r="G74" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H74" s="12" t="s">
@@ -3447,7 +3669,7 @@
       <c r="D75" s="22"/>
       <c r="E75" s="17"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="73"/>
+      <c r="G75" s="72"/>
       <c r="H75" s="12"/>
       <c r="I75" s="44"/>
     </row>
@@ -3471,17 +3693,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3518,430 +3740,992 @@
       <c r="A2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="58"/>
+      <c r="B2" s="54">
+        <v>46357</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="56">
+        <v>3450214834</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="58" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="54">
+        <v>46357</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="64">
+        <v>3450189160</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I3" s="44" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="22">
+        <v>136138608</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450209147</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I4" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="44"/>
+      <c r="B5" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="22">
+        <v>136205150</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450214515</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="22">
+        <v>136236485</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450216760</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="I6" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="22">
+        <v>136242492</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450217309</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="22">
+        <v>136237016</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450216935</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="22">
+        <v>136237898</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450216968</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="22">
+        <v>136245655</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450217595</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I10" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="7">
+        <v>46038</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="22">
+        <v>136249313</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450217936</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="76" t="s">
+        <v>144</v>
+      </c>
+      <c r="I11" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="22">
+        <v>136251637</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450218211</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="22">
+        <v>136258778</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450218541</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="22">
+        <v>136197660</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450213888</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G14" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="22">
+        <v>136263011</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450218937</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="22">
+        <v>136256269</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450218409</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G16" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="7">
+        <v>46032</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="22">
+        <v>136192409</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450213668</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I17" s="44">
+        <v>46032</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="22">
+        <v>136241303</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450217155</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G18" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46038</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="22">
+        <v>136295931</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450221423</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="44">
+        <v>46038</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>46041</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="22">
+        <v>136310665</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450222380</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" s="44">
+        <v>46041</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>46020</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="22">
+        <v>136078351</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450200116</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G21" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="I21" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="22">
+        <v>136142232</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450209422</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="44"/>
+      <c r="B23" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C23" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="22">
+        <v>136143250</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450209500</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="44"/>
+      <c r="B24" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="22">
+        <v>136248476</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450217837</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="G24" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="I24" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="44"/>
+      <c r="B25" s="7">
+        <v>46038</v>
+      </c>
+      <c r="C25" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="22">
+        <v>136135971</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450208641</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="I25" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="44"/>
+      <c r="B26" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C26" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="22">
+        <v>136137403</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450208850</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="44">
+        <v>46044</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="44"/>
+      <c r="B27" s="7">
+        <v>46040</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="22">
+        <v>136100653</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450205484</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="44"/>
+      <c r="B28" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="22">
+        <v>136131576</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450208256</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="I28" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="44"/>
+      <c r="B29" s="7">
+        <v>46052</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="22">
+        <v>136134008</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450208410</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G29" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="76" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="B30" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="22">
+        <v>136245494</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450217584</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="76" t="s">
+        <v>177</v>
+      </c>
+      <c r="I30" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="B31" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C31" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="22">
+        <v>136143609</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450209543</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="B32" s="7">
+        <v>46054</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="22">
+        <v>136204550</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450214460</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="I32" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="24"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C33" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="22">
+        <v>136206999</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450214669</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="I33" s="44">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C34" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="22">
+        <v>136283913</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450219740</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I34" s="44">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="44"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="44"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F32">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A36" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6975,6 +7759,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540083</_dlc_DocId>
@@ -7017,66 +7810,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14537913923f18b595a8efb93d476f56">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c805678a1a23774ee476d175eb06e332" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7454,18 +8188,68 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E01D7C-4C26-49E2-83EE-F31B8251D9DB}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E01D7C-4C26-49E2-83EE-F31B8251D9DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D0DE081-1949-4CF0-B38E-6F4866006899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{523CFD45-633A-44CB-B03E-0C012B7254FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="19.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="227">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -670,6 +670,165 @@
   </si>
   <si>
     <t xml:space="preserve">RAFAEL NETO DA SILVA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANILSON SOBREIRA DE SOUZA                   </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE houve quebra de vigência de 61 dias e não houve sinist
+ro , conforme regra reduz 1 classes de bônus, assim sendo o corret
+o bônus 0.
+Com a correção ficou 10x R$ 348,79. Podemos emitir
+desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREY OEIRAS PEDROSO                        </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 20.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAX GUILHERME DE ANDRADE E SILVA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Painel com a motocicleta desligada (luz de oleo acionada) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARISA GOMES DO CARMO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ANTONIO MORELLI                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA HELENA DE SOUZA E SILVA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSEFA INACIO DE SOUZA PAGLIUSO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDGARD NICEAS ARCOVERDE GUSMAO LIMA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATA DAIANE ZARA                           </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve quebra de vigência de 76 dias e não houve sinistr
+o , conforme regra reduz 1 classes de bônus, assim sendo o correto
+bônus0.
+Com a correção ficou 10x R$ 515,46. Podemos emitir de
+sta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCA SOLUCOES EM TRANSPORTES LTDA EPP         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: Motor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELBY ALVES CARRIJO                          </t>
+  </si>
+  <si>
+    <t>É necessária apresentação de um laudo válido que consiste em avali
+ar a situação estrutural do veículo (carroceria, colunas, longarin
+as, torre do amortecedor, painel corta fogo etc.) e também a parte
+da avaliação administrativa e documental do Laudo Cautelar, que c
+onsiste emavaliar (licenciamento, restrições (tributária/judicia
+l/financeira/renajud ) , dívidas, multas , roubo e furto, recall,
+passagens em leilões etc.) .
+Vale ressaltar que a Allianz não a
+rca com as custas deste Laudo
+IMPORTANTE: Antes da realização d
+a vistoria, confirmar se o laudo atende os requisitos acima e a va
+lidade, que deve ser de até 30 dias.
+Os laudos realizados passa
+rão por uma análiseda Cia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURILO OLIVEIRA ROCHA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: Frente e lateral do passageiro e motorista enquadrando a placa do veiculo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSSET IMPLEMENTOS AMBIENTAIS LTDA EPP       </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro, conforme regra diminui uma class
+e de bônus, assim sendo o correto bônus 0.
+Com a correção fico
+u 10x R$ 573,69. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAJUA SAMIR ASAD GHANI                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotos que tiveram repique: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUREA MARIA MOREIRA DOS SANTOS               </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+– Cópia da apólice congênere c
+om vigência de 2026 a 2027.
+– Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULA KARINA DAMASCENO                       </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Frente e lateral do passageiro, Chassi, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERESA CRISTINA PETRY MARTINS PEREIRA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELENIR CUCHI                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIO PASSOS DE OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t>Não enviou todas as fotos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO FERREIRA DOS REIS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILBERTO DE JESUS ALVES BAPTISTA             </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Chassi, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLENE SARTORETTO                           </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Documento do veículo, Chassi, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t>15/01/2026</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMBO </t>
+  </si>
+  <si>
+    <t>CLIENTE CILENE SILVA SANTANA CPF 11472624890</t>
+  </si>
+  <si>
+    <t>Cliente não cancelou apólice ativa</t>
   </si>
 </sst>
 </file>
@@ -971,7 +1130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1130,12 +1289,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1144,9 +1297,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1168,6 +1318,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1560,10 +1714,10 @@
       <c r="D2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="70">
+      <c r="E2" s="67">
         <v>3450214746</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="68" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="42" t="s">
@@ -1584,13 +1738,13 @@
       <c r="C3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="62">
         <v>3450220246</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="63" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="42" t="s">
@@ -1622,7 +1776,7 @@
       <c r="F4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="45" t="s">
@@ -1651,7 +1805,7 @@
       <c r="F5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="69" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="45" t="s">
@@ -1680,7 +1834,7 @@
       <c r="F6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="72" t="s">
+      <c r="G6" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="45" t="s">
@@ -1709,7 +1863,7 @@
       <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="45" t="s">
@@ -1738,7 +1892,7 @@
       <c r="F8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="G8" s="69" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="45" t="s">
@@ -1767,7 +1921,7 @@
       <c r="F9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="45" t="s">
@@ -1796,7 +1950,7 @@
       <c r="F10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="45" t="s">
@@ -1825,7 +1979,7 @@
       <c r="F11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -1854,7 +2008,7 @@
       <c r="F12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="72" t="s">
+      <c r="G12" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H12" s="45" t="s">
@@ -1883,7 +2037,7 @@
       <c r="F13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="G13" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="45" t="s">
@@ -1912,7 +2066,7 @@
       <c r="F14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="72" t="s">
+      <c r="G14" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="45" t="s">
@@ -1941,7 +2095,7 @@
       <c r="F15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="72" t="s">
+      <c r="G15" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H15" s="45" t="s">
@@ -1970,7 +2124,7 @@
       <c r="F16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="72" t="s">
+      <c r="G16" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H16" s="45" t="s">
@@ -1999,7 +2153,7 @@
       <c r="F17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="72" t="s">
+      <c r="G17" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H17" s="45" t="s">
@@ -2028,7 +2182,7 @@
       <c r="F18" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="72" t="s">
+      <c r="G18" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="45" t="s">
@@ -2057,7 +2211,7 @@
       <c r="F19" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="G19" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H19" s="45" t="s">
@@ -2086,7 +2240,7 @@
       <c r="F20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H20" s="45" t="s">
@@ -2115,7 +2269,7 @@
       <c r="F21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="72" t="s">
+      <c r="G21" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="45" t="s">
@@ -2144,7 +2298,7 @@
       <c r="F22" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="72" t="s">
+      <c r="G22" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H22" s="45" t="s">
@@ -2173,7 +2327,7 @@
       <c r="F23" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="72" t="s">
+      <c r="G23" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H23" s="45" t="s">
@@ -2202,7 +2356,7 @@
       <c r="F24" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="72" t="s">
+      <c r="G24" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H24" s="45" t="s">
@@ -2231,7 +2385,7 @@
       <c r="F25" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="72" t="s">
+      <c r="G25" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H25" s="45" t="s">
@@ -2260,7 +2414,7 @@
       <c r="F26" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="72" t="s">
+      <c r="G26" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H26" s="45" t="s">
@@ -2289,7 +2443,7 @@
       <c r="F27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="72" t="s">
+      <c r="G27" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H27" s="45" t="s">
@@ -2318,7 +2472,7 @@
       <c r="F28" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="72" t="s">
+      <c r="G28" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="45" t="s">
@@ -2347,7 +2501,7 @@
       <c r="F29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="72" t="s">
+      <c r="G29" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H29" s="45" t="s">
@@ -2376,7 +2530,7 @@
       <c r="F30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="72" t="s">
+      <c r="G30" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H30" s="45" t="s">
@@ -2405,7 +2559,7 @@
       <c r="F31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="72" t="s">
+      <c r="G31" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H31" s="45" t="s">
@@ -2434,7 +2588,7 @@
       <c r="F32" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G32" s="72" t="s">
+      <c r="G32" s="69" t="s">
         <v>69</v>
       </c>
       <c r="H32" s="45" t="s">
@@ -2463,7 +2617,7 @@
       <c r="F33" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="72" t="s">
+      <c r="G33" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H33" s="45" t="s">
@@ -2492,7 +2646,7 @@
       <c r="F34" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="72" t="s">
+      <c r="G34" s="69" t="s">
         <v>13</v>
       </c>
       <c r="H34" s="45" t="s">
@@ -2521,7 +2675,7 @@
       <c r="F35" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G35" s="72" t="s">
+      <c r="G35" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H35" s="45" t="s">
@@ -2550,7 +2704,7 @@
       <c r="F36" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="72" t="s">
+      <c r="G36" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H36" s="45" t="s">
@@ -2579,7 +2733,7 @@
       <c r="F37" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="72" t="s">
+      <c r="G37" s="69" t="s">
         <v>13</v>
       </c>
       <c r="H37" s="45" t="s">
@@ -2608,7 +2762,7 @@
       <c r="F38" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="72" t="s">
+      <c r="G38" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="45" t="s">
@@ -2637,7 +2791,7 @@
       <c r="F39" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G39" s="72" t="s">
+      <c r="G39" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="45" t="s">
@@ -2666,7 +2820,7 @@
       <c r="F40" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G40" s="72" t="s">
+      <c r="G40" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="45" t="s">
@@ -2695,7 +2849,7 @@
       <c r="F41" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="72" t="s">
+      <c r="G41" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H41" s="45" t="s">
@@ -2724,7 +2878,7 @@
       <c r="F42" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G42" s="72" t="s">
+      <c r="G42" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H42" s="45" t="s">
@@ -2753,7 +2907,7 @@
       <c r="F43" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G43" s="72" t="s">
+      <c r="G43" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H43" s="45" t="s">
@@ -2782,7 +2936,7 @@
       <c r="F44" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="72" t="s">
+      <c r="G44" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H44" s="45" t="s">
@@ -2811,7 +2965,7 @@
       <c r="F45" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G45" s="72" t="s">
+      <c r="G45" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H45" s="45" t="s">
@@ -2840,7 +2994,7 @@
       <c r="F46" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G46" s="72" t="s">
+      <c r="G46" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H46" s="45" t="s">
@@ -2869,7 +3023,7 @@
       <c r="F47" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G47" s="72" t="s">
+      <c r="G47" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H47" s="45" t="s">
@@ -2898,7 +3052,7 @@
       <c r="F48" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G48" s="72" t="s">
+      <c r="G48" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H48" s="45" t="s">
@@ -2927,7 +3081,7 @@
       <c r="F49" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="72" t="s">
+      <c r="G49" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H49" s="45" t="s">
@@ -2956,7 +3110,7 @@
       <c r="F50" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G50" s="72" t="s">
+      <c r="G50" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H50" s="45" t="s">
@@ -2985,7 +3139,7 @@
       <c r="F51" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G51" s="72" t="s">
+      <c r="G51" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H51" s="45" t="s">
@@ -3014,7 +3168,7 @@
       <c r="F52" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G52" s="72" t="s">
+      <c r="G52" s="69" t="s">
         <v>69</v>
       </c>
       <c r="H52" s="45" t="s">
@@ -3043,7 +3197,7 @@
       <c r="F53" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G53" s="72" t="s">
+      <c r="G53" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H53" s="45" t="s">
@@ -3072,7 +3226,7 @@
       <c r="F54" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="72" t="s">
+      <c r="G54" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H54" s="45" t="s">
@@ -3101,7 +3255,7 @@
       <c r="F55" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G55" s="72" t="s">
+      <c r="G55" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H55" s="45" t="s">
@@ -3130,7 +3284,7 @@
       <c r="F56" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G56" s="72" t="s">
+      <c r="G56" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H56" s="45" t="s">
@@ -3159,7 +3313,7 @@
       <c r="F57" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G57" s="72" t="s">
+      <c r="G57" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H57" s="45" t="s">
@@ -3188,7 +3342,7 @@
       <c r="F58" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="72" t="s">
+      <c r="G58" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H58" s="45" t="s">
@@ -3217,7 +3371,7 @@
       <c r="F59" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G59" s="72" t="s">
+      <c r="G59" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H59" s="45" t="s">
@@ -3246,7 +3400,7 @@
       <c r="F60" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G60" s="74" t="s">
+      <c r="G60" s="71" t="s">
         <v>26</v>
       </c>
       <c r="H60" s="45" t="s">
@@ -3275,7 +3429,7 @@
       <c r="F61" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G61" s="72" t="s">
+      <c r="G61" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="45" t="s">
@@ -3304,7 +3458,7 @@
       <c r="F62" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="72" t="s">
+      <c r="G62" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H62" s="45" t="s">
@@ -3333,7 +3487,7 @@
       <c r="F63" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G63" s="72" t="s">
+      <c r="G63" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H63" s="45" t="s">
@@ -3362,7 +3516,7 @@
       <c r="F64" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G64" s="72" t="s">
+      <c r="G64" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H64" s="45" t="s">
@@ -3391,7 +3545,7 @@
       <c r="F65" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G65" s="72" t="s">
+      <c r="G65" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H65" s="45" t="s">
@@ -3420,7 +3574,7 @@
       <c r="F66" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G66" s="72" t="s">
+      <c r="G66" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H66" s="12" t="s">
@@ -3449,7 +3603,7 @@
       <c r="F67" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G67" s="72" t="s">
+      <c r="G67" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H67" s="12" t="s">
@@ -3478,7 +3632,7 @@
       <c r="F68" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G68" s="72" t="s">
+      <c r="G68" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H68" s="12" t="s">
@@ -3507,7 +3661,7 @@
       <c r="F69" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G69" s="72" t="s">
+      <c r="G69" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H69" s="12" t="s">
@@ -3536,7 +3690,7 @@
       <c r="F70" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G70" s="72" t="s">
+      <c r="G70" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="12" t="s">
@@ -3565,7 +3719,7 @@
       <c r="F71" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G71" s="72" t="s">
+      <c r="G71" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H71" s="12" t="s">
@@ -3594,7 +3748,7 @@
       <c r="F72" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G72" s="72" t="s">
+      <c r="G72" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H72" s="12" t="s">
@@ -3623,7 +3777,7 @@
       <c r="F73" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G73" s="72" t="s">
+      <c r="G73" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H73" s="12" t="s">
@@ -3652,7 +3806,7 @@
       <c r="F74" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G74" s="72" t="s">
+      <c r="G74" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H74" s="12" t="s">
@@ -3669,7 +3823,7 @@
       <c r="D75" s="22"/>
       <c r="E75" s="17"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="72"/>
+      <c r="G75" s="69"/>
       <c r="H75" s="12"/>
       <c r="I75" s="44"/>
     </row>
@@ -3775,13 +3929,13 @@
       <c r="C3" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="62">
         <v>3450189160</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="63" t="s">
         <v>127</v>
       </c>
       <c r="G3" s="42" t="s">
@@ -3813,7 +3967,7 @@
       <c r="F4" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="69" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="12" t="s">
@@ -3842,7 +3996,7 @@
       <c r="F5" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H5" s="12" t="s">
@@ -3871,7 +4025,7 @@
       <c r="F6" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="72" t="s">
+      <c r="G6" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H6" s="12" t="s">
@@ -3900,7 +4054,7 @@
       <c r="F7" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="11" t="s">
@@ -3929,7 +4083,7 @@
       <c r="F8" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="G8" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="11" t="s">
@@ -3958,7 +4112,7 @@
       <c r="F9" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H9" s="12" t="s">
@@ -3987,7 +4141,7 @@
       <c r="F10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -4016,10 +4170,10 @@
       <c r="F11" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="76" t="s">
+      <c r="H11" s="12" t="s">
         <v>144</v>
       </c>
       <c r="I11" s="44">
@@ -4045,7 +4199,7 @@
       <c r="F12" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="72" t="s">
+      <c r="G12" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -4074,7 +4228,7 @@
       <c r="F13" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="G13" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -4103,7 +4257,7 @@
       <c r="F14" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="72" t="s">
+      <c r="G14" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H14" s="12" t="s">
@@ -4132,7 +4286,7 @@
       <c r="F15" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="72" t="s">
+      <c r="G15" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="12" t="s">
@@ -4161,7 +4315,7 @@
       <c r="F16" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G16" s="72" t="s">
+      <c r="G16" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -4190,7 +4344,7 @@
       <c r="F17" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G17" s="72" t="s">
+      <c r="G17" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="12" t="s">
@@ -4219,7 +4373,7 @@
       <c r="F18" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="G18" s="72" t="s">
+      <c r="G18" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H18" s="12" t="s">
@@ -4248,7 +4402,7 @@
       <c r="F19" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="G19" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="12" t="s">
@@ -4277,7 +4431,7 @@
       <c r="F20" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="12" t="s">
@@ -4306,7 +4460,7 @@
       <c r="F21" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="72" t="s">
+      <c r="G21" s="69" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="12" t="s">
@@ -4335,7 +4489,7 @@
       <c r="F22" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G22" s="72" t="s">
+      <c r="G22" s="69" t="s">
         <v>69</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -4364,7 +4518,7 @@
       <c r="F23" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="G23" s="72" t="s">
+      <c r="G23" s="69" t="s">
         <v>69</v>
       </c>
       <c r="H23" s="12" t="s">
@@ -4393,7 +4547,7 @@
       <c r="F24" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="72" t="s">
+      <c r="G24" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H24" s="12" t="s">
@@ -4422,10 +4576,10 @@
       <c r="F25" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G25" s="72" t="s">
+      <c r="G25" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="76" t="s">
+      <c r="H25" s="12" t="s">
         <v>167</v>
       </c>
       <c r="I25" s="44">
@@ -4451,10 +4605,10 @@
       <c r="F26" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="72" t="s">
+      <c r="G26" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="76" t="s">
+      <c r="H26" s="12" t="s">
         <v>169</v>
       </c>
       <c r="I26" s="44">
@@ -4480,10 +4634,10 @@
       <c r="F27" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G27" s="72" t="s">
+      <c r="G27" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="76" t="s">
+      <c r="H27" s="12" t="s">
         <v>171</v>
       </c>
       <c r="I27" s="44">
@@ -4509,10 +4663,10 @@
       <c r="F28" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="G28" s="72" t="s">
+      <c r="G28" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="76" t="s">
+      <c r="H28" s="12" t="s">
         <v>173</v>
       </c>
       <c r="I28" s="44">
@@ -4538,10 +4692,10 @@
       <c r="F29" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="G29" s="72" t="s">
+      <c r="G29" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="76" t="s">
+      <c r="H29" s="12" t="s">
         <v>175</v>
       </c>
       <c r="I29" s="44">
@@ -4567,10 +4721,10 @@
       <c r="F30" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="72" t="s">
+      <c r="G30" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="76" t="s">
+      <c r="H30" s="12" t="s">
         <v>177</v>
       </c>
       <c r="I30" s="44">
@@ -4596,10 +4750,10 @@
       <c r="F31" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="72" t="s">
+      <c r="G31" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="76" t="s">
+      <c r="H31" s="12" t="s">
         <v>179</v>
       </c>
       <c r="I31" s="44">
@@ -4625,10 +4779,10 @@
       <c r="F32" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="G32" s="72" t="s">
+      <c r="G32" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="76" t="s">
+      <c r="H32" s="12" t="s">
         <v>181</v>
       </c>
       <c r="I32" s="44">
@@ -4654,7 +4808,7 @@
       <c r="F33" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="G33" s="72" t="s">
+      <c r="G33" s="69" t="s">
         <v>35</v>
       </c>
       <c r="H33" s="12" t="s">
@@ -4683,7 +4837,7 @@
       <c r="F34" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="G34" s="72" t="s">
+      <c r="G34" s="69" t="s">
         <v>47</v>
       </c>
       <c r="H34" s="12" t="s">
@@ -4735,13 +4889,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25" style="16" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="30.5703125" style="16" customWidth="1"/>
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
@@ -4781,472 +4936,697 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="44"/>
+      <c r="B2" s="60">
+        <v>46030</v>
+      </c>
+      <c r="C2" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D2" s="22">
+        <v>136168042</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450211435</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="60">
+        <v>46036</v>
+      </c>
+      <c r="C3" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D3" s="22">
+        <v>136235650</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450216858</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="60">
+        <v>46040</v>
+      </c>
+      <c r="C4" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D4" s="22">
+        <v>136240866</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450217111</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="48"/>
+      <c r="B5" s="60">
+        <v>46037</v>
+      </c>
+      <c r="C5" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D5" s="22">
+        <v>136259760</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450218629</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="I5" s="48">
+        <v>46037</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="60">
+        <v>46037</v>
+      </c>
+      <c r="C6" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D6" s="22">
+        <v>136272873</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450219916</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="60">
+        <v>46037</v>
+      </c>
+      <c r="C7" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D7" s="22">
+        <v>136267964</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450219400</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="60">
+        <v>46036</v>
+      </c>
+      <c r="C8" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D8" s="22">
+        <v>136247223</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450217750</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="60">
+        <v>46037</v>
+      </c>
+      <c r="C9" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D9" s="22">
+        <v>136285232</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450219619</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="69" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="60"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="60">
+        <v>46042</v>
+      </c>
+      <c r="C10" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D10" s="22">
+        <v>136328294</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450223590</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="44">
+        <v>46043</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="60"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="60">
+        <v>46034</v>
+      </c>
+      <c r="C11" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D11" s="22">
+        <v>136204484</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450214449</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="I11" s="44">
+        <v>46041</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="60">
+        <v>46037</v>
+      </c>
+      <c r="C12" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D12" s="22">
+        <v>136261498</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450218740</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="G12" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="I12" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="60">
+        <v>46030</v>
+      </c>
+      <c r="C13" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D13" s="22">
+        <v>136155031</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450210005</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G13" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="I13" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="60">
+        <v>46037</v>
+      </c>
+      <c r="C14" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D14" s="22">
+        <v>136268608</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450219509</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I14" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="60">
+        <v>46030</v>
+      </c>
+      <c r="C15" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D15" s="22">
+        <v>136161590</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450210720</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I15" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="60">
+        <v>46037</v>
+      </c>
+      <c r="C16" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D16" s="22">
+        <v>136263581</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450219025</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I16" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="7">
+        <v>46032</v>
+      </c>
+      <c r="C17" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D17" s="22">
+        <v>136156332</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450210280</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="75" t="s">
+        <v>209</v>
+      </c>
+      <c r="I17" s="44">
+        <v>46037</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C18" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D18" s="22">
+        <v>136237446</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450216946</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G18" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="I18" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C19" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D19" s="22">
+        <v>136250722</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450218080</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G19" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I19" s="44">
+        <v>46036</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>46041</v>
+      </c>
+      <c r="C20" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D20" s="22">
+        <v>136343395</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450221698</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G20" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" s="44">
+        <v>46041</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C21" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D21" s="22">
+        <v>136267310</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450219366</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G21" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I21" s="48">
+        <v>46037</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C22" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D22" s="22">
+        <v>136157001</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450210335</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G22" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C23" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D23" s="22">
+        <v>136241493</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450215450</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="I23" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C24" s="25">
+        <v>46043</v>
+      </c>
+      <c r="D24" s="22">
+        <v>136239432</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450215934</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="I24" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
+      <c r="D25" s="22"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="44"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A25" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G25" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B16" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5301,14 +5681,30 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="B2" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" s="8">
+        <v>3450218431</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -7759,60 +8155,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540083</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540083</Url>
-      <Description>QAFFA7D2F2TC-2102087286-540083</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14537913923f18b595a8efb93d476f56">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c805678a1a23774ee476d175eb06e332" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="06364c42bcbf61016b6bd5e32d4d0782">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="199c6c2eefa6ec2f672a95412cfea747" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -7851,6 +8195,7 @@
                 <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns3:_Flow_SignoffStatus" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -8088,6 +8433,11 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="40" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
     <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
@@ -8188,7 +8538,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -8238,18 +8588,70 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540083</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540083</Url>
+      <Description>QAFFA7D2F2TC-2102087286-540083</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EB5007-F016-4E17-BC8B-56A069F0892C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E01D7C-4C26-49E2-83EE-F31B8251D9DB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{523CFD45-633A-44CB-B03E-0C012B7254FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85F3D12A-CD89-41B9-AA88-FA1B07A26B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="19.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="249">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -829,6 +829,85 @@
   </si>
   <si>
     <t>Cliente não cancelou apólice ativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS CARLOS DA SILVA                         </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 21.01.2026</t>
+  </si>
+  <si>
+    <t>J E F E M COMERCIO DE TINTAS E SERVICOS DE OB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA BEATRIZ VIANNA TEIXEIRA                  </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Frente e lateral do passageiro, Chassi, Motor e placa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAROLINE MENEZES OLIVEIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPS SERVICOS OFFSHORE LTDA EPP               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">YANNA A A SILVA ME                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCUS DI OSTI VIEIRA                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que
+a apólice consta ativa na congênere, para que possamos prossegui
+r coma liberação do bloqueio será necessário a apresentação do e
+ndosso de cancelamento emitido, a atualização junto a Central de B
+ônus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA GARCIA RISSO GONCALVES               </t>
+  </si>
+  <si>
+    <t>Conforme CBE houve sinistro na apólice anterior, portanto a renova
+ção correta é externa COM sinistro, conforme regra diminui uma cla
+sse debônus, assim sendo o correto bônus “ 00 “.
+Com a correçã
+o ficou 10x R$ 755,41. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCILIO RODRIGUES DA SILVA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ROBERTO BRITO                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada n
+a congênere de origem. Portanto, peço a gentileza de encaminhar a
+documentação abaixo para análise:
+– Cópia da apólice congênere
+com vigência de 2026 a 2027;
+– Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE DANIEL DE BERTO SOUSA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESAU SILVA                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARALICE NUNES DO NASCIMENTO MOREIRA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINALDO PIZANE DE AZEVEDO                  </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Documento do veículo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CLAUDIA BEZERRA JANEIRO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO EXPIRADO FOTOS: Frente e lateral do passageiro, Chassi, Frente e lateral do motorista</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1196,9 +1275,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1322,6 +1398,20 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1711,22 +1801,22 @@
       <c r="C2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="67">
+      <c r="E2" s="66">
         <v>3450214746</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1738,22 +1828,22 @@
       <c r="C3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="62">
+      <c r="E3" s="61">
         <v>3450220246</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="43" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1776,13 +1866,13 @@
       <c r="F4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -1805,13 +1895,13 @@
       <c r="F5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -1834,13 +1924,13 @@
       <c r="F6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -1863,13 +1953,13 @@
       <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -1892,13 +1982,13 @@
       <c r="F8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="69" t="s">
+      <c r="G8" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -1921,13 +2011,13 @@
       <c r="F9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -1950,13 +2040,13 @@
       <c r="F10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="69" t="s">
+      <c r="G10" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -1979,13 +2069,13 @@
       <c r="F11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="G11" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -2008,13 +2098,13 @@
       <c r="F12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="69" t="s">
+      <c r="G12" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -2037,13 +2127,13 @@
       <c r="F13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="69" t="s">
+      <c r="G13" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -2066,13 +2156,13 @@
       <c r="F14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="69" t="s">
+      <c r="G14" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -2095,13 +2185,13 @@
       <c r="F15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -2124,13 +2214,13 @@
       <c r="F16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -2153,13 +2243,13 @@
       <c r="F17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -2182,13 +2272,13 @@
       <c r="F18" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2211,13 +2301,13 @@
       <c r="F19" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2240,13 +2330,13 @@
       <c r="F20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2269,13 +2359,13 @@
       <c r="F21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="69" t="s">
+      <c r="G21" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -2298,13 +2388,13 @@
       <c r="F22" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="69" t="s">
+      <c r="G22" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2327,13 +2417,13 @@
       <c r="F23" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="69" t="s">
+      <c r="G23" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -2356,13 +2446,13 @@
       <c r="F24" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="69" t="s">
+      <c r="G24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2385,13 +2475,13 @@
       <c r="F25" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="69" t="s">
+      <c r="G25" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="H25" s="45" t="s">
+      <c r="H25" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -2414,13 +2504,13 @@
       <c r="F26" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="69" t="s">
+      <c r="G26" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -2443,13 +2533,13 @@
       <c r="F27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="69" t="s">
+      <c r="G27" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -2472,13 +2562,13 @@
       <c r="F28" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="69" t="s">
+      <c r="G28" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -2501,13 +2591,13 @@
       <c r="F29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="69" t="s">
+      <c r="G29" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -2530,13 +2620,13 @@
       <c r="F30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="69" t="s">
+      <c r="G30" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="45" t="s">
+      <c r="H30" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -2559,13 +2649,13 @@
       <c r="F31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="69" t="s">
+      <c r="G31" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -2588,13 +2678,13 @@
       <c r="F32" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G32" s="69" t="s">
+      <c r="G32" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -2617,13 +2707,13 @@
       <c r="F33" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="69" t="s">
+      <c r="G33" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="I33" s="48">
+      <c r="I33" s="47">
         <v>46035</v>
       </c>
     </row>
@@ -2646,13 +2736,13 @@
       <c r="F34" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="69" t="s">
+      <c r="G34" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="45" t="s">
+      <c r="H34" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -2675,13 +2765,13 @@
       <c r="F35" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G35" s="69" t="s">
+      <c r="G35" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -2704,13 +2794,13 @@
       <c r="F36" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="69" t="s">
+      <c r="G36" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="45" t="s">
+      <c r="H36" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2733,13 +2823,13 @@
       <c r="F37" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="69" t="s">
+      <c r="G37" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="45" t="s">
+      <c r="H37" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -2762,13 +2852,13 @@
       <c r="F38" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="69" t="s">
+      <c r="G38" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -2791,13 +2881,13 @@
       <c r="F39" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G39" s="69" t="s">
+      <c r="G39" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="45" t="s">
+      <c r="H39" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -2820,13 +2910,13 @@
       <c r="F40" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G40" s="69" t="s">
+      <c r="G40" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H40" s="45" t="s">
+      <c r="H40" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -2849,13 +2939,13 @@
       <c r="F41" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="69" t="s">
+      <c r="G41" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="45" t="s">
+      <c r="H41" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2878,13 +2968,13 @@
       <c r="F42" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G42" s="69" t="s">
+      <c r="G42" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="45" t="s">
+      <c r="H42" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="43">
         <v>46028</v>
       </c>
     </row>
@@ -2907,13 +2997,13 @@
       <c r="F43" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G43" s="69" t="s">
+      <c r="G43" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H43" s="45" t="s">
+      <c r="H43" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="43">
         <v>46028</v>
       </c>
     </row>
@@ -2936,13 +3026,13 @@
       <c r="F44" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="69" t="s">
+      <c r="G44" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="45" t="s">
+      <c r="H44" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -2965,13 +3055,13 @@
       <c r="F45" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G45" s="69" t="s">
+      <c r="G45" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="45" t="s">
+      <c r="H45" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="43">
         <v>46029</v>
       </c>
     </row>
@@ -2994,13 +3084,13 @@
       <c r="F46" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G46" s="69" t="s">
+      <c r="G46" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="45" t="s">
+      <c r="H46" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="43">
         <v>46028</v>
       </c>
     </row>
@@ -3023,13 +3113,13 @@
       <c r="F47" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G47" s="69" t="s">
+      <c r="G47" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H47" s="45" t="s">
+      <c r="H47" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="43">
         <v>46029</v>
       </c>
     </row>
@@ -3052,13 +3142,13 @@
       <c r="F48" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G48" s="69" t="s">
+      <c r="G48" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H48" s="45" t="s">
+      <c r="H48" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="43">
         <v>46029</v>
       </c>
     </row>
@@ -3081,13 +3171,13 @@
       <c r="F49" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="69" t="s">
+      <c r="G49" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H49" s="45" t="s">
+      <c r="H49" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="43">
         <v>46014</v>
       </c>
     </row>
@@ -3110,13 +3200,13 @@
       <c r="F50" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G50" s="69" t="s">
+      <c r="G50" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H50" s="45" t="s">
+      <c r="H50" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="43">
         <v>46029</v>
       </c>
     </row>
@@ -3139,13 +3229,13 @@
       <c r="F51" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G51" s="69" t="s">
+      <c r="G51" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H51" s="45" t="s">
+      <c r="H51" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="43">
         <v>46029</v>
       </c>
     </row>
@@ -3168,13 +3258,13 @@
       <c r="F52" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G52" s="69" t="s">
+      <c r="G52" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="H52" s="45" t="s">
+      <c r="H52" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3197,13 +3287,13 @@
       <c r="F53" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G53" s="69" t="s">
+      <c r="G53" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="45" t="s">
+      <c r="H53" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -3226,13 +3316,13 @@
       <c r="F54" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="69" t="s">
+      <c r="G54" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H54" s="45" t="s">
+      <c r="H54" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="43">
         <v>46029</v>
       </c>
     </row>
@@ -3255,13 +3345,13 @@
       <c r="F55" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G55" s="69" t="s">
+      <c r="G55" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H55" s="45" t="s">
+      <c r="H55" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="43">
         <v>46029</v>
       </c>
     </row>
@@ -3284,13 +3374,13 @@
       <c r="F56" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G56" s="69" t="s">
+      <c r="G56" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H56" s="45" t="s">
+      <c r="H56" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I56" s="44">
+      <c r="I56" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3313,13 +3403,13 @@
       <c r="F57" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G57" s="69" t="s">
+      <c r="G57" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H57" s="45" t="s">
+      <c r="H57" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3342,13 +3432,13 @@
       <c r="F58" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="69" t="s">
+      <c r="G58" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H58" s="45" t="s">
+      <c r="H58" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3371,13 +3461,13 @@
       <c r="F59" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G59" s="69" t="s">
+      <c r="G59" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H59" s="45" t="s">
+      <c r="H59" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3400,13 +3490,13 @@
       <c r="F60" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G60" s="71" t="s">
+      <c r="G60" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="H60" s="45" t="s">
+      <c r="H60" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3429,13 +3519,13 @@
       <c r="F61" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G61" s="69" t="s">
+      <c r="G61" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H61" s="45" t="s">
+      <c r="H61" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3458,13 +3548,13 @@
       <c r="F62" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="69" t="s">
+      <c r="G62" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H62" s="45" t="s">
+      <c r="H62" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I62" s="58">
+      <c r="I62" s="57">
         <v>46030</v>
       </c>
     </row>
@@ -3487,13 +3577,13 @@
       <c r="F63" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G63" s="69" t="s">
+      <c r="G63" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H63" s="45" t="s">
+      <c r="H63" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3516,13 +3606,13 @@
       <c r="F64" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G64" s="69" t="s">
+      <c r="G64" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="45" t="s">
+      <c r="H64" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3530,7 +3620,7 @@
       <c r="A65" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="47">
+      <c r="B65" s="46">
         <v>46030</v>
       </c>
       <c r="C65" s="25" t="s">
@@ -3545,13 +3635,13 @@
       <c r="F65" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G65" s="69" t="s">
+      <c r="G65" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H65" s="45" t="s">
+      <c r="H65" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I65" s="44">
+      <c r="I65" s="43">
         <v>46030</v>
       </c>
     </row>
@@ -3574,13 +3664,13 @@
       <c r="F66" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G66" s="69" t="s">
+      <c r="G66" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I66" s="44">
+      <c r="I66" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3603,13 +3693,13 @@
       <c r="F67" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G67" s="69" t="s">
+      <c r="G67" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I67" s="44">
+      <c r="I67" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3632,13 +3722,13 @@
       <c r="F68" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G68" s="69" t="s">
+      <c r="G68" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H68" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I68" s="44">
+      <c r="I68" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3661,13 +3751,13 @@
       <c r="F69" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G69" s="69" t="s">
+      <c r="G69" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I69" s="44">
+      <c r="I69" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3690,13 +3780,13 @@
       <c r="F70" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G70" s="69" t="s">
+      <c r="G70" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I70" s="44">
+      <c r="I70" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3719,13 +3809,13 @@
       <c r="F71" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G71" s="69" t="s">
+      <c r="G71" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H71" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I71" s="44">
+      <c r="I71" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3748,13 +3838,13 @@
       <c r="F72" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G72" s="69" t="s">
+      <c r="G72" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I72" s="44">
+      <c r="I72" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3777,13 +3867,13 @@
       <c r="F73" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G73" s="69" t="s">
+      <c r="G73" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I73" s="44">
+      <c r="I73" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3806,13 +3896,13 @@
       <c r="F74" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G74" s="69" t="s">
+      <c r="G74" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I74" s="44">
+      <c r="I74" s="43">
         <v>46031</v>
       </c>
     </row>
@@ -3823,9 +3913,9 @@
       <c r="D75" s="22"/>
       <c r="E75" s="17"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="69"/>
+      <c r="G75" s="68"/>
       <c r="H75" s="12"/>
-      <c r="I75" s="44"/>
+      <c r="I75" s="43"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -3862,60 +3952,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="49" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="54">
+      <c r="A2" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="53">
         <v>46357</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="56">
+      <c r="E2" s="55">
         <v>3450214834</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3923,28 +4013,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B3" s="53">
         <v>46357</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="62">
+      <c r="E3" s="61">
         <v>3450189160</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>69</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="43" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3955,7 +4045,7 @@
       <c r="B4" s="7">
         <v>46042</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D4" s="22">
@@ -3967,13 +4057,13 @@
       <c r="F4" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3984,7 +4074,7 @@
       <c r="B5" s="7">
         <v>46034</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D5" s="22">
@@ -3996,13 +4086,13 @@
       <c r="F5" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -4013,7 +4103,7 @@
       <c r="B6" s="7">
         <v>46035</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D6" s="22">
@@ -4025,13 +4115,13 @@
       <c r="F6" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -4042,7 +4132,7 @@
       <c r="B7" s="7">
         <v>46036</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D7" s="22">
@@ -4054,13 +4144,13 @@
       <c r="F7" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4071,7 +4161,7 @@
       <c r="B8" s="7">
         <v>46036</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D8" s="22">
@@ -4083,13 +4173,13 @@
       <c r="F8" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="69" t="s">
+      <c r="G8" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4100,7 +4190,7 @@
       <c r="B9" s="7">
         <v>46036</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D9" s="22">
@@ -4112,13 +4202,13 @@
       <c r="F9" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4129,7 +4219,7 @@
       <c r="B10" s="7">
         <v>46036</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D10" s="22">
@@ -4141,13 +4231,13 @@
       <c r="F10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="G10" s="69" t="s">
+      <c r="G10" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4158,7 +4248,7 @@
       <c r="B11" s="7">
         <v>46038</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D11" s="22">
@@ -4170,13 +4260,13 @@
       <c r="F11" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="G11" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -4187,7 +4277,7 @@
       <c r="B12" s="7">
         <v>46036</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D12" s="22">
@@ -4199,13 +4289,13 @@
       <c r="F12" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="69" t="s">
+      <c r="G12" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4216,7 +4306,7 @@
       <c r="B13" s="7">
         <v>46037</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D13" s="22">
@@ -4228,13 +4318,13 @@
       <c r="F13" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="69" t="s">
+      <c r="G13" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4245,7 +4335,7 @@
       <c r="B14" s="7">
         <v>46034</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D14" s="22">
@@ -4257,13 +4347,13 @@
       <c r="F14" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="69" t="s">
+      <c r="G14" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -4274,7 +4364,7 @@
       <c r="B15" s="7">
         <v>46037</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D15" s="22">
@@ -4286,13 +4376,13 @@
       <c r="F15" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="68" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4303,7 +4393,7 @@
       <c r="B16" s="7">
         <v>46037</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D16" s="22">
@@ -4315,13 +4405,13 @@
       <c r="F16" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4332,7 +4422,7 @@
       <c r="B17" s="7">
         <v>46032</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D17" s="22">
@@ -4344,13 +4434,13 @@
       <c r="F17" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>46032</v>
       </c>
     </row>
@@ -4361,7 +4451,7 @@
       <c r="B18" s="7">
         <v>46036</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="22">
@@ -4373,13 +4463,13 @@
       <c r="F18" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4390,7 +4480,7 @@
       <c r="B19" s="7">
         <v>46038</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="C19" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D19" s="22">
@@ -4402,13 +4492,13 @@
       <c r="F19" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="68" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -4419,7 +4509,7 @@
       <c r="B20" s="7">
         <v>46041</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="C20" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D20" s="22">
@@ -4431,13 +4521,13 @@
       <c r="F20" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="68" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -4448,7 +4538,7 @@
       <c r="B21" s="7">
         <v>46020</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D21" s="22">
@@ -4460,13 +4550,13 @@
       <c r="F21" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="69" t="s">
+      <c r="G21" s="68" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -4477,7 +4567,7 @@
       <c r="B22" s="7">
         <v>46029</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D22" s="22">
@@ -4489,13 +4579,13 @@
       <c r="F22" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G22" s="69" t="s">
+      <c r="G22" s="68" t="s">
         <v>69</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -4506,7 +4596,7 @@
       <c r="B23" s="7">
         <v>46029</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D23" s="22">
@@ -4518,13 +4608,13 @@
       <c r="F23" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="G23" s="69" t="s">
+      <c r="G23" s="68" t="s">
         <v>69</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -4535,7 +4625,7 @@
       <c r="B24" s="7">
         <v>46036</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="22">
@@ -4547,13 +4637,13 @@
       <c r="F24" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="69" t="s">
+      <c r="G24" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4564,7 +4654,7 @@
       <c r="B25" s="7">
         <v>46038</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D25" s="22">
@@ -4576,13 +4666,13 @@
       <c r="F25" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G25" s="69" t="s">
+      <c r="G25" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -4593,7 +4683,7 @@
       <c r="B26" s="7">
         <v>46044</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D26" s="22">
@@ -4605,13 +4695,13 @@
       <c r="F26" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="69" t="s">
+      <c r="G26" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>46044</v>
       </c>
     </row>
@@ -4622,7 +4712,7 @@
       <c r="B27" s="7">
         <v>46040</v>
       </c>
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D27" s="22">
@@ -4634,13 +4724,13 @@
       <c r="F27" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G27" s="69" t="s">
+      <c r="G27" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -4651,7 +4741,7 @@
       <c r="B28" s="7">
         <v>46029</v>
       </c>
-      <c r="C28" s="55" t="s">
+      <c r="C28" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D28" s="22">
@@ -4663,13 +4753,13 @@
       <c r="F28" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="G28" s="69" t="s">
+      <c r="G28" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -4680,7 +4770,7 @@
       <c r="B29" s="7">
         <v>46052</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D29" s="22">
@@ -4692,13 +4782,13 @@
       <c r="F29" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="G29" s="69" t="s">
+      <c r="G29" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -4709,7 +4799,7 @@
       <c r="B30" s="7">
         <v>46044</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="C30" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D30" s="22">
@@ -4721,13 +4811,13 @@
       <c r="F30" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="69" t="s">
+      <c r="G30" s="68" t="s">
         <v>17</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -4738,7 +4828,7 @@
       <c r="B31" s="7">
         <v>46029</v>
       </c>
-      <c r="C31" s="55" t="s">
+      <c r="C31" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D31" s="22">
@@ -4750,13 +4840,13 @@
       <c r="F31" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="69" t="s">
+      <c r="G31" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4767,7 +4857,7 @@
       <c r="B32" s="7">
         <v>46054</v>
       </c>
-      <c r="C32" s="55" t="s">
+      <c r="C32" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D32" s="22">
@@ -4779,13 +4869,13 @@
       <c r="F32" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="G32" s="69" t="s">
+      <c r="G32" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4796,7 +4886,7 @@
       <c r="B33" s="7">
         <v>46034</v>
       </c>
-      <c r="C33" s="55" t="s">
+      <c r="C33" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D33" s="22">
@@ -4808,13 +4898,13 @@
       <c r="F33" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="G33" s="69" t="s">
+      <c r="G33" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="43">
         <v>46034</v>
       </c>
     </row>
@@ -4825,7 +4915,7 @@
       <c r="B34" s="7">
         <v>46037</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="C34" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D34" s="22">
@@ -4837,37 +4927,37 @@
       <c r="F34" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="G34" s="69" t="s">
+      <c r="G34" s="68" t="s">
         <v>47</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>46037</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="42"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="41"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="55"/>
+      <c r="C36" s="54"/>
       <c r="D36" s="22"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
+      <c r="G36" s="41"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="43"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -4897,7 +4987,7 @@
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" style="16" customWidth="1"/>
     <col min="5" max="5" width="30.5703125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
     <col min="9" max="9" width="21" style="24" customWidth="1"/>
@@ -4928,7 +5018,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4936,7 +5026,7 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="60">
+      <c r="B2" s="59">
         <v>46030</v>
       </c>
       <c r="C2" s="25">
@@ -4954,10 +5044,10 @@
       <c r="G2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="44">
+      <c r="I2" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4965,7 +5055,7 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="59">
         <v>46036</v>
       </c>
       <c r="C3" s="25">
@@ -4983,10 +5073,10 @@
       <c r="G3" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -4994,7 +5084,7 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="59">
         <v>46040</v>
       </c>
       <c r="C4" s="25">
@@ -5012,10 +5102,10 @@
       <c r="G4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -5023,7 +5113,7 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="59">
         <v>46037</v>
       </c>
       <c r="C5" s="25">
@@ -5038,13 +5128,13 @@
       <c r="F5" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="65" t="s">
+      <c r="H5" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="47">
         <v>46037</v>
       </c>
     </row>
@@ -5052,7 +5142,7 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="59">
         <v>46037</v>
       </c>
       <c r="C6" s="25">
@@ -5067,13 +5157,13 @@
       <c r="F6" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5081,7 +5171,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="59">
         <v>46037</v>
       </c>
       <c r="C7" s="25">
@@ -5096,13 +5186,13 @@
       <c r="F7" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="68" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -5110,7 +5200,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="59">
         <v>46036</v>
       </c>
       <c r="C8" s="25">
@@ -5125,13 +5215,13 @@
       <c r="F8" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="G8" s="69" t="s">
+      <c r="G8" s="68" t="s">
         <v>26</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -5139,7 +5229,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="60">
+      <c r="B9" s="59">
         <v>46037</v>
       </c>
       <c r="C9" s="25">
@@ -5154,13 +5244,13 @@
       <c r="F9" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="68" t="s">
         <v>47</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5168,7 +5258,7 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="59">
         <v>46042</v>
       </c>
       <c r="C10" s="25">
@@ -5183,13 +5273,13 @@
       <c r="F10" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="72" t="s">
         <v>13</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -5197,7 +5287,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="59">
         <v>46034</v>
       </c>
       <c r="C11" s="25">
@@ -5212,13 +5302,13 @@
       <c r="F11" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -5226,7 +5316,7 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="59">
         <v>46037</v>
       </c>
       <c r="C12" s="25">
@@ -5241,13 +5331,13 @@
       <c r="F12" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="G12" s="69" t="s">
+      <c r="G12" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5255,7 +5345,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="59">
         <v>46030</v>
       </c>
       <c r="C13" s="25">
@@ -5270,13 +5360,13 @@
       <c r="F13" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="G13" s="69" t="s">
+      <c r="G13" s="68" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5284,7 +5374,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="60">
+      <c r="B14" s="59">
         <v>46037</v>
       </c>
       <c r="C14" s="25">
@@ -5299,13 +5389,13 @@
       <c r="F14" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="72" t="s">
         <v>35</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5313,7 +5403,7 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="60">
+      <c r="B15" s="59">
         <v>46030</v>
       </c>
       <c r="C15" s="25">
@@ -5328,13 +5418,13 @@
       <c r="F15" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="68" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5342,7 +5432,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="60">
+      <c r="B16" s="59">
         <v>46037</v>
       </c>
       <c r="C16" s="25">
@@ -5357,13 +5447,13 @@
       <c r="F16" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5386,13 +5476,13 @@
       <c r="F17" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="75" t="s">
+      <c r="H17" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -5415,13 +5505,13 @@
       <c r="F18" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -5444,13 +5534,13 @@
       <c r="F19" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -5473,13 +5563,13 @@
       <c r="F20" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="72" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -5502,13 +5592,13 @@
       <c r="F21" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="G21" s="69" t="s">
+      <c r="G21" s="68" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="47">
         <v>46037</v>
       </c>
     </row>
@@ -5531,13 +5621,13 @@
       <c r="F22" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="G22" s="66" t="s">
+      <c r="G22" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="61" t="s">
+      <c r="H22" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -5563,10 +5653,10 @@
       <c r="G23" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="74" t="s">
+      <c r="H23" s="73" t="s">
         <v>219</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -5592,10 +5682,10 @@
       <c r="G24" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="74" t="s">
+      <c r="H24" s="73" t="s">
         <v>221</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>46035</v>
       </c>
     </row>
@@ -5607,8 +5697,8 @@
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
       <c r="G25" s="21"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="44"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="43"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -5634,17 +5724,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" customWidth="1"/>
+    <col min="8" max="8" width="31.5703125" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5687,22 +5777,22 @@
       <c r="C2" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="77" t="s">
         <v>224</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="13">
         <v>3450218431</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="43" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5710,203 +5800,447 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="24"/>
+      <c r="B3" s="25">
+        <v>46037</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="78">
+        <v>136259803</v>
+      </c>
+      <c r="E3" s="76">
+        <v>3450218630</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I3" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="B4" s="25">
+        <v>46037</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" s="78">
+        <v>136265038</v>
+      </c>
+      <c r="E4" s="76">
+        <v>3450219179</v>
+      </c>
+      <c r="F4" s="75" t="s">
+        <v>229</v>
+      </c>
+      <c r="G4" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="43">
+        <v>46037</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="B5" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="78">
+        <v>136268873</v>
+      </c>
+      <c r="E5" s="76">
+        <v>3450219520</v>
+      </c>
+      <c r="F5" s="75" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="I5" s="43">
+        <v>46037</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="B6" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="78">
+        <v>136323633</v>
+      </c>
+      <c r="E6" s="76">
+        <v>3450223150</v>
+      </c>
+      <c r="F6" s="75" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I6" s="43">
+        <v>46042</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="24"/>
+      <c r="B7" s="7">
+        <v>46043</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="78">
+        <v>136346545</v>
+      </c>
+      <c r="E7" s="76">
+        <v>3450224680</v>
+      </c>
+      <c r="F7" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="G7" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="24"/>
+      <c r="B8" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="78">
+        <v>136283841</v>
+      </c>
+      <c r="E8" s="76">
+        <v>3450218717</v>
+      </c>
+      <c r="F8" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="43">
+        <v>46037</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="24"/>
+      <c r="B9" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="78">
+        <v>136189133</v>
+      </c>
+      <c r="E9" s="76">
+        <v>3450213459</v>
+      </c>
+      <c r="F9" s="75" t="s">
+        <v>235</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="80" t="s">
+        <v>236</v>
+      </c>
+      <c r="I9" s="43">
+        <v>46035</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="24"/>
+      <c r="B10" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D10" s="78">
+        <v>136190909</v>
+      </c>
+      <c r="E10" s="76">
+        <v>3450213569</v>
+      </c>
+      <c r="F10" s="75" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="80" t="s">
+        <v>238</v>
+      </c>
+      <c r="I10" s="43">
+        <v>46031</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="24"/>
+      <c r="B11" s="7">
+        <v>46038</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="78">
+        <v>136284770</v>
+      </c>
+      <c r="E11" s="76">
+        <v>3450220576</v>
+      </c>
+      <c r="F11" s="75" t="s">
+        <v>239</v>
+      </c>
+      <c r="G11" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="43">
+        <v>46038</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="24"/>
+      <c r="B12" s="7">
+        <v>46049</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="78">
+        <v>136187231</v>
+      </c>
+      <c r="E12" s="76">
+        <v>3450213283</v>
+      </c>
+      <c r="F12" s="75" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="I12" s="43">
+        <v>46035</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="24"/>
+      <c r="B13" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="78">
+        <v>136279831</v>
+      </c>
+      <c r="E13" s="76">
+        <v>3450217210</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>242</v>
+      </c>
+      <c r="G13" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I13" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="24"/>
+      <c r="B14" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="78">
+        <v>136258212</v>
+      </c>
+      <c r="E14" s="76">
+        <v>3450218520</v>
+      </c>
+      <c r="F14" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="G14" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I14" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="24"/>
+      <c r="B15" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="78">
+        <v>136180926</v>
+      </c>
+      <c r="E15" s="76">
+        <v>3450212612</v>
+      </c>
+      <c r="F15" s="75" t="s">
+        <v>244</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="80" t="s">
+        <v>179</v>
+      </c>
+      <c r="I15" s="43">
+        <v>46038</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="24"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46038</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D16" s="78">
+        <v>136276674</v>
+      </c>
+      <c r="E16" s="76">
+        <v>3450220004</v>
+      </c>
+      <c r="F16" s="75" t="s">
+        <v>245</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="I16" s="43">
+        <v>46038</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="24"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D17" s="78">
+        <v>136261227</v>
+      </c>
+      <c r="E17" s="76">
+        <v>3450216979</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>247</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="I17" s="43">
+        <v>46036</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="D18" s="20"/>
       <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="24"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -5915,9 +6249,9 @@
       <c r="D19" s="8"/>
       <c r="E19" s="13"/>
       <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="79"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5926,9 +6260,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5938,7 +6272,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="12"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -5948,7 +6283,8 @@
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="12"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -5958,7 +6294,8 @@
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -5968,7 +6305,8 @@
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="12"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -5978,7 +6316,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="12"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -5988,7 +6327,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="12"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -5998,7 +6338,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="12"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -6008,7 +6349,8 @@
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="12"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -6018,7 +6360,8 @@
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="12"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -6028,269 +6371,20 @@
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A17" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G30" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6366,7 +6460,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="33"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -6399,8 +6493,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="24"/>
@@ -6930,7 +7024,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6946,8 +7040,8 @@
       <c r="D2" s="22"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="33"/>
       <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9">
@@ -6959,8 +7053,8 @@
       <c r="D3" s="22"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="33"/>
       <c r="I3" s="24"/>
     </row>
     <row r="4" spans="1:9">
@@ -6972,8 +7066,8 @@
       <c r="D4" s="22"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="33"/>
       <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9">
@@ -6985,8 +7079,8 @@
       <c r="D5" s="22"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="35"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="34"/>
       <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9">
@@ -6998,8 +7092,8 @@
       <c r="D6" s="22"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="36"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9">
@@ -7011,8 +7105,8 @@
       <c r="D7" s="22"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9">
@@ -7024,8 +7118,8 @@
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="36"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9">
@@ -7037,8 +7131,8 @@
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="34"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:9">
@@ -7050,8 +7144,8 @@
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="34"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9">
@@ -7063,8 +7157,8 @@
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="34"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="24"/>
     </row>
     <row r="12" spans="1:9">
@@ -7076,8 +7170,8 @@
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="34"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="33"/>
       <c r="I12" s="24"/>
     </row>
     <row r="13" spans="1:9">
@@ -7089,8 +7183,8 @@
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="34"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:9">
@@ -7102,8 +7196,8 @@
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="34"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9">
@@ -7115,8 +7209,8 @@
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9">
@@ -7128,12 +7222,12 @@
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="33"/>
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
@@ -7141,8 +7235,8 @@
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="24"/>
     </row>
     <row r="18" spans="1:9">
@@ -7154,8 +7248,8 @@
       <c r="D18" s="22"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="34"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9">
@@ -7163,9 +7257,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="28"/>
       <c r="H19" s="9"/>
       <c r="I19" s="24"/>
     </row>
@@ -7176,7 +7270,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="28"/>
       <c r="H20" s="9"/>
       <c r="I20" s="24"/>
     </row>
@@ -7187,7 +7281,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
+      <c r="G21" s="28"/>
       <c r="H21" s="9"/>
       <c r="I21" s="24"/>
     </row>
@@ -7198,7 +7292,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
+      <c r="G22" s="28"/>
       <c r="H22" s="9"/>
       <c r="I22" s="24"/>
     </row>
@@ -7209,7 +7303,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="28"/>
       <c r="H23" s="9"/>
       <c r="I23" s="24"/>
     </row>
@@ -7220,7 +7314,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="28"/>
       <c r="H24" s="9"/>
       <c r="I24" s="24"/>
     </row>
@@ -7634,12 +7728,12 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="25"/>
-      <c r="D2" s="43"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -7647,12 +7741,12 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="25"/>
-      <c r="D3" s="43"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="44"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -7660,12 +7754,12 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="25"/>
-      <c r="D4" s="43"/>
+      <c r="D4" s="42"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -7673,12 +7767,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="25"/>
-      <c r="D5" s="43"/>
+      <c r="D5" s="42"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="44"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -7686,12 +7780,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="25"/>
-      <c r="D6" s="43"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="44"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -7699,12 +7793,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="25"/>
-      <c r="D7" s="43"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="44"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -7712,12 +7806,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="25"/>
-      <c r="D8" s="43"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -7725,12 +7819,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="25"/>
-      <c r="D9" s="43"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="44"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -7738,12 +7832,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="25"/>
-      <c r="D10" s="43"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="44"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -7751,12 +7845,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="25"/>
-      <c r="D11" s="43"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="44"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -7764,12 +7858,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="25"/>
-      <c r="D12" s="43"/>
+      <c r="D12" s="42"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -7777,12 +7871,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="43"/>
+      <c r="D13" s="42"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -7790,12 +7884,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="25"/>
-      <c r="D14" s="43"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -7803,12 +7897,12 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="43"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
@@ -7816,25 +7910,25 @@
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="43"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="43"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
@@ -7842,285 +7936,285 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="43"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="43"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="44"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="43"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="44"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="43"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="44"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="25"/>
-      <c r="D22" s="43"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="44"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="43"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="43"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="44"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="43"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="25"/>
-      <c r="D24" s="43"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="44"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="43"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="43"/>
+      <c r="D25" s="42"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="44"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="25"/>
-      <c r="D26" s="43"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="44"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="43"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="44"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="43"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="25"/>
-      <c r="D28" s="43"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="44"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="47"/>
+      <c r="B29" s="46"/>
       <c r="C29" s="25"/>
-      <c r="D29" s="43"/>
+      <c r="D29" s="42"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="44"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="25"/>
-      <c r="D30" s="43"/>
+      <c r="D30" s="42"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="25"/>
-      <c r="D31" s="43"/>
+      <c r="D31" s="42"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="25"/>
-      <c r="D32" s="43"/>
+      <c r="D32" s="42"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="I32" s="43"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="25"/>
-      <c r="D33" s="43"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="42"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="44"/>
+      <c r="I33" s="43"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="43"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="44"/>
+      <c r="I34" s="43"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="43"/>
+      <c r="D35" s="42"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="42"/>
+      <c r="G35" s="41"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="25"/>
-      <c r="D36" s="43"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
+      <c r="G36" s="41"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="43"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="43"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
+      <c r="G37" s="41"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="44"/>
+      <c r="I37" s="43"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
       <c r="C38" s="25"/>
-      <c r="D38" s="43"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="42"/>
+      <c r="G38" s="41"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="25"/>
-      <c r="D39" s="43"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="42"/>
+      <c r="G39" s="41"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="43"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="25"/>
-      <c r="D40" s="43"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
+      <c r="G40" s="41"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="44"/>
+      <c r="I40" s="43"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="25"/>
-      <c r="D41" s="43"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="42"/>
+      <c r="G41" s="41"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="44"/>
+      <c r="I41" s="43"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
       <c r="C42" s="25"/>
-      <c r="D42" s="43"/>
+      <c r="D42" s="42"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="42"/>
+      <c r="G42" s="41"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="44"/>
+      <c r="I42" s="43"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="29"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="42"/>
+      <c r="G43" s="41"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -8155,6 +8249,58 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540083</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540083</Url>
+      <Description>QAFFA7D2F2TC-2102087286-540083</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="06364c42bcbf61016b6bd5e32d4d0782">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="199c6c2eefa6ec2f672a95412cfea747" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8538,7 +8684,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -8588,70 +8734,18 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540083</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540083</Url>
-      <Description>QAFFA7D2F2TC-2102087286-540083</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EB5007-F016-4E17-BC8B-56A069F0892C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 19.01.2026 a 25.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85F3D12A-CD89-41B9-AA88-FA1B07A26B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8797A3B7-B7DC-4481-860C-B0F4264B2B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="19.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="304">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -908,6 +908,199 @@
   </si>
   <si>
     <t xml:space="preserve"> SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO EXPIRADO FOTOS: Frente e lateral do passageiro, Chassi, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENAN AUGUSTO RODRIGUES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILMO CRISPIN DE OLIVEIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALTER MIGUEL ROMAO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAIANE TEIXEIRA DOS SANTOS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDECI ZANOLE DE OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFIO LTDA ME                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA LUCIA MAGNO RYGAARD DA SILVA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Frente e lateral do passageiro, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHAEL JUNIO SOTERO                         </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senho
+r(a) MICHAEL JUNIO SOTERO, pois este não consta como condutor na a
+pólice anterior.
+Neste caso estamos nesta data efetuando a re
+cusa desta proposta. Orientamos transmitir um novo processo como S
+eguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARYAM SEGRETO SICHI                         </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 22.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHAEL JOSEPH COLEMAN                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINICIOS SOARES DE SA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z S CONTRUCOES LTDA ME                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUREA APARECIDA GOMES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ TOLEDO NETO                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRA VIANA TEIXEIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE CARLOS BARAUNA DA SILVA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARI APARECIDO RODRIGUES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUDGARDA MARTINS FIGUEREDO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIRIAM PATRICIO ARACATI                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDNA DE MEDEIROS MORAIS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTO CARLOS GOMES DA SILVA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO BARBOZA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D P ESTEVO LTDA ME                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAIR CORCINO MENDES                          </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO, FOTO DO HODOMETRO DESLIGADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WANDERSON PAULINO DO NASCIMENTO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAN LUCAS DA SILVA NEVES                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M B DE FREITAS FERNANDES PAREDES ME          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE EDUARDO DE SOUSA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NILZA MARIA BENEIS                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO DANIEL MOLYNEAUX SANTOS                </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senho
+r(a) FABIO DANIEL MOLYNEAUX SANTOS , pois este não consta como con
+dutor na apólice anterior.
+Neste caso, iremos realizar a recu
+sa desta proposta, para conclusão do processo é necessário informa
+r o emaildo segurado anterior (PAULA KARINA DAMASCENO), para que o
+mesmo também fique ciente da recusa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO SILVA SOARES                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANA KOTZENT                              </t>
+  </si>
+  <si>
+    <t>A própria congênere através da Central de Bônus informa que houve
+renovação. Pedimos que entrem em contato com eles e nos enviem os
+documentos necessários para seguirmos com a emissão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOLO DIONE DA PAIXAO CAETANO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA SIQUEIRA ZAFRA DE MELO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME DE REZENDE LOPES                   </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE trata-se de renovação fora do prazo, sendo renovada co
+m 175 dias em atraso e não houve sinistro , conforme regra reduz 4
+classes de bônus, assim sendo o correto bônus 6.
+Com a correçã
+o ficou 10x R$ 380,40. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAGNER PINHEIRO DA CRUZ                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA BERNADETE PRUDENCIO DE ARAUJO          </t>
+  </si>
+  <si>
+    <t>Informamos que a p
+roposta em questão se encontra em duplicidade com a apólice 517720
+2542312847609, para prosseguirmos com a emissão se faz necessário
+realizar o cancelamento dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA IZABEL TEIXEIRA BORGES                 </t>
+  </si>
+  <si>
+    <t>CI INVÁLIDA
+Favor enviar cópia completa d
+a apólice anterior 2025/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONALDO DE OLIVEIRA MARQUES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME ALVES CARVALHO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE WELLINGTON SANTOS PINHEIRO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL MESSIAS ALVES BRITO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAIS DE OLIVEIRA DIAS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CICERO FERREIRA NETO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA FRANCISCA GARCIA BRANDAO               </t>
+  </si>
+  <si>
+    <t>Informamos que a pr
+oposta em questão se encontra em duplicidade com a apolice 5177202
+551311099577, para prosseguirmos com a emissão se faz necessário r
+ealizar o cancelamento da mesma.</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1071,19 +1264,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1204,12 +1384,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1236,7 +1436,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1252,9 +1451,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1267,7 +1463,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1282,50 +1478,23 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1346,34 +1515,34 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1382,36 +1551,64 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1798,25 +1995,25 @@
       <c r="B2" s="7">
         <v>46034</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="66">
+      <c r="E2" s="53">
         <v>3450214746</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="43"/>
+      <c r="I2" s="30"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1825,25 +2022,25 @@
       <c r="B3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="61">
+      <c r="E3" s="48">
         <v>3450220246</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="30" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1854,25 +2051,25 @@
       <c r="B4" s="7">
         <v>46028</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>136105116</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <v>3450205946</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -1883,25 +2080,25 @@
       <c r="B5" s="7">
         <v>46030</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <v>136162103</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>3450210841</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -1912,25 +2109,25 @@
       <c r="B6" s="7">
         <v>46030</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <v>136162072</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <v>3450210820</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -1941,25 +2138,25 @@
       <c r="B7" s="7">
         <v>46030</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <v>136167809</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>3450211402</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -1970,25 +2167,25 @@
       <c r="B8" s="7">
         <v>46030</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <v>136166035</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="16">
         <v>3450211248</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -1999,25 +2196,25 @@
       <c r="B9" s="7">
         <v>46031</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <v>136174298</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>3450211853</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -2028,25 +2225,25 @@
       <c r="B10" s="7">
         <v>46031</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>136175680</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>3450211985</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -2057,25 +2254,25 @@
       <c r="B11" s="7">
         <v>46030</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="20">
         <v>136164243</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>3450211072</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -2086,25 +2283,25 @@
       <c r="B12" s="7">
         <v>46031</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <v>136198766</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>3450211941</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -2115,25 +2312,25 @@
       <c r="B13" s="7">
         <v>46034</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>136201029</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>3450214174</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -2144,25 +2341,25 @@
       <c r="B14" s="7">
         <v>46030</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <v>136161353</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>3450210698</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -2173,25 +2370,25 @@
       <c r="B15" s="7">
         <v>46034</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <v>136209773</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="16">
         <v>3450214944</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G15" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -2202,25 +2399,25 @@
       <c r="B16" s="7">
         <v>46034</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <v>136203437</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>3450214372</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="68" t="s">
+      <c r="G16" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -2231,25 +2428,25 @@
       <c r="B17" s="7">
         <v>46034</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <v>136209760</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="16">
         <v>3450214933</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -2260,25 +2457,25 @@
       <c r="B18" s="7">
         <v>46035</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <v>136227274</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="16">
         <v>3450216320</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="68" t="s">
+      <c r="G18" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -2289,25 +2486,25 @@
       <c r="B19" s="7">
         <v>46035</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <v>136220573</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>3450215681</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -2318,25 +2515,25 @@
       <c r="B20" s="7">
         <v>46035</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <v>136216117</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="16">
         <v>3450215362</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="68" t="s">
+      <c r="G20" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -2347,25 +2544,25 @@
       <c r="B21" s="7">
         <v>46034</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <v>136196673</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="16">
         <v>3450213811</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="G21" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -2376,25 +2573,25 @@
       <c r="B22" s="7">
         <v>46035</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <v>136227805</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="16">
         <v>3450216374</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="68" t="s">
+      <c r="G22" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -2405,25 +2602,25 @@
       <c r="B23" s="7">
         <v>46036</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <v>136239888</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>3450217067</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="68" t="s">
+      <c r="G23" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -2434,25 +2631,25 @@
       <c r="B24" s="7">
         <v>46035</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="20">
         <v>136220049</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>3450215637</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="G24" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -2463,25 +2660,25 @@
       <c r="B25" s="7">
         <v>46037</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="20">
         <v>136264765</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="16">
         <v>3450219146</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="G25" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -2492,25 +2689,25 @@
       <c r="B26" s="7">
         <v>46037</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="20">
         <v>136266207</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="16">
         <v>3450219234</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="68" t="s">
+      <c r="G26" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -2521,25 +2718,25 @@
       <c r="B27" s="7">
         <v>46031</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="20">
         <v>136181906</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="16">
         <v>3450212722</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="68" t="s">
+      <c r="G27" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -2550,25 +2747,25 @@
       <c r="B28" s="7">
         <v>46047</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="20">
         <v>136126331</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="16">
         <v>3450207816</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="68" t="s">
+      <c r="G28" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H28" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -2579,25 +2776,25 @@
       <c r="B29" s="7">
         <v>46034</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="20">
         <v>136203766</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="16">
         <v>3450214405</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="68" t="s">
+      <c r="G29" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="H29" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -2608,25 +2805,25 @@
       <c r="B30" s="7">
         <v>46038</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="20">
         <v>136284827</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="16">
         <v>3450220598</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="68" t="s">
+      <c r="G30" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="44" t="s">
+      <c r="H30" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -2637,25 +2834,25 @@
       <c r="B31" s="7">
         <v>46036</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="20">
         <v>136238433</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>3450216980</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="G31" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H31" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -2666,25 +2863,25 @@
       <c r="B32" s="7">
         <v>46031</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="20">
         <v>136115118</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>3450206419</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G32" s="68" t="s">
+      <c r="G32" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="H32" s="44" t="s">
+      <c r="H32" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -2695,25 +2892,25 @@
       <c r="B33" s="7">
         <v>46035</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="20">
         <v>136220894</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="16">
         <v>3450215736</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="68" t="s">
+      <c r="G33" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="I33" s="47">
+      <c r="I33" s="34">
         <v>46035</v>
       </c>
     </row>
@@ -2724,25 +2921,25 @@
       <c r="B34" s="7">
         <v>46034</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="20">
         <v>136216946</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="16">
         <v>3450214240</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="68" t="s">
+      <c r="G34" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="44" t="s">
+      <c r="H34" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -2753,25 +2950,25 @@
       <c r="B35" s="7">
         <v>46034</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="20">
         <v>136209535</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="16">
         <v>3450214911</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G35" s="68" t="s">
+      <c r="G35" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="H35" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -2782,25 +2979,25 @@
       <c r="B36" s="7">
         <v>46035</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="20">
         <v>136229601</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="16">
         <v>3450216561</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="68" t="s">
+      <c r="G36" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="44" t="s">
+      <c r="H36" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -2811,25 +3008,25 @@
       <c r="B37" s="7">
         <v>46031</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="20">
         <v>136121181</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="16">
         <v>3450207090</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="68" t="s">
+      <c r="G37" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -2840,25 +3037,25 @@
       <c r="B38" s="7">
         <v>46038</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="20">
         <v>136117926</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="16">
         <v>3450206727</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="68" t="s">
+      <c r="G38" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -2869,25 +3066,25 @@
       <c r="B39" s="7">
         <v>46031</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="20">
         <v>136120139</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="16">
         <v>3450206958</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G39" s="68" t="s">
+      <c r="G39" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="44" t="s">
+      <c r="H39" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -2898,25 +3095,25 @@
       <c r="B40" s="7">
         <v>46029</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="20">
         <v>136121993</v>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="16">
         <v>3450207156</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G40" s="68" t="s">
+      <c r="G40" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H40" s="44" t="s">
+      <c r="H40" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -2927,25 +3124,25 @@
       <c r="B41" s="7">
         <v>46035</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="20">
         <v>136219683</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="20">
         <v>3450215582</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="68" t="s">
+      <c r="G41" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -2956,25 +3153,25 @@
       <c r="B42" s="7">
         <v>46028</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="20">
         <v>136124148</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="20">
         <v>3450207453</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G42" s="68" t="s">
+      <c r="G42" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="44" t="s">
+      <c r="H42" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="30">
         <v>46028</v>
       </c>
     </row>
@@ -2985,25 +3182,25 @@
       <c r="B43" s="7">
         <v>46028</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C43" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="20">
         <v>136127037</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="20">
         <v>3450207926</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="G43" s="68" t="s">
+      <c r="G43" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H43" s="44" t="s">
+      <c r="H43" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="I43" s="43">
+      <c r="I43" s="30">
         <v>46028</v>
       </c>
     </row>
@@ -3014,25 +3211,25 @@
       <c r="B44" s="7">
         <v>46035</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C44" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="20">
         <v>136225063</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="20">
         <v>3450216143</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="68" t="s">
+      <c r="G44" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="44" t="s">
+      <c r="H44" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="I44" s="43">
+      <c r="I44" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -3043,25 +3240,25 @@
       <c r="B45" s="7">
         <v>46029</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="20">
         <v>136130942</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="20">
         <v>3450208212</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G45" s="68" t="s">
+      <c r="G45" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="43">
+      <c r="I45" s="30">
         <v>46029</v>
       </c>
     </row>
@@ -3072,25 +3269,25 @@
       <c r="B46" s="7">
         <v>46028</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="20">
         <v>136131146</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="20">
         <v>3450206530</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="G46" s="68" t="s">
+      <c r="G46" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="44" t="s">
+      <c r="H46" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I46" s="43">
+      <c r="I46" s="30">
         <v>46028</v>
       </c>
     </row>
@@ -3101,25 +3298,25 @@
       <c r="B47" s="7">
         <v>46029</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="20">
         <v>136132033</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="20">
         <v>3450208290</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G47" s="68" t="s">
+      <c r="G47" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H47" s="44" t="s">
+      <c r="H47" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I47" s="43">
+      <c r="I47" s="30">
         <v>46029</v>
       </c>
     </row>
@@ -3130,25 +3327,25 @@
       <c r="B48" s="7">
         <v>46029</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="20">
         <v>136133116</v>
       </c>
-      <c r="E48" s="22">
+      <c r="E48" s="20">
         <v>3450208333</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="G48" s="68" t="s">
+      <c r="G48" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H48" s="44" t="s">
+      <c r="H48" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="30">
         <v>46029</v>
       </c>
     </row>
@@ -3159,25 +3356,25 @@
       <c r="B49" s="7">
         <v>46014</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="20">
         <v>136134361</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="20">
         <v>3450195793</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="68" t="s">
+      <c r="G49" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H49" s="44" t="s">
+      <c r="H49" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I49" s="43">
+      <c r="I49" s="30">
         <v>46014</v>
       </c>
     </row>
@@ -3188,25 +3385,25 @@
       <c r="B50" s="7">
         <v>46029</v>
       </c>
-      <c r="C50" s="25" t="s">
+      <c r="C50" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="20">
         <v>136137429</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E50" s="20">
         <v>3450208861</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="G50" s="68" t="s">
+      <c r="G50" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H50" s="44" t="s">
+      <c r="H50" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I50" s="43">
+      <c r="I50" s="30">
         <v>46029</v>
       </c>
     </row>
@@ -3217,25 +3414,25 @@
       <c r="B51" s="7">
         <v>46029</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="20">
         <v>136137680</v>
       </c>
-      <c r="E51" s="22">
+      <c r="E51" s="20">
         <v>3450208993</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="G51" s="68" t="s">
+      <c r="G51" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H51" s="44" t="s">
+      <c r="H51" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I51" s="43">
+      <c r="I51" s="30">
         <v>46029</v>
       </c>
     </row>
@@ -3246,25 +3443,25 @@
       <c r="B52" s="7">
         <v>46029</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="20">
         <v>136140242</v>
       </c>
-      <c r="E52" s="22">
+      <c r="E52" s="20">
         <v>3450209280</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="G52" s="68" t="s">
+      <c r="G52" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="H52" s="44" t="s">
+      <c r="H52" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="I52" s="43">
+      <c r="I52" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -3275,25 +3472,25 @@
       <c r="B53" s="7">
         <v>46020</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C53" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="20">
         <v>136150239</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E53" s="20">
         <v>3450200182</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="G53" s="68" t="s">
+      <c r="G53" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="44" t="s">
+      <c r="H53" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I53" s="43">
+      <c r="I53" s="30">
         <v>46020</v>
       </c>
     </row>
@@ -3304,25 +3501,25 @@
       <c r="B54" s="7">
         <v>46029</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="20">
         <v>136153470</v>
       </c>
-      <c r="E54" s="22">
+      <c r="E54" s="20">
         <v>3450208784</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="68" t="s">
+      <c r="G54" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H54" s="44" t="s">
+      <c r="H54" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I54" s="43">
+      <c r="I54" s="30">
         <v>46029</v>
       </c>
     </row>
@@ -3333,25 +3530,25 @@
       <c r="B55" s="7">
         <v>46029</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="20">
         <v>136155363</v>
       </c>
-      <c r="E55" s="22">
+      <c r="E55" s="20">
         <v>3450209312</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="G55" s="68" t="s">
+      <c r="G55" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H55" s="44" t="s">
+      <c r="H55" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I55" s="43">
+      <c r="I55" s="30">
         <v>46029</v>
       </c>
     </row>
@@ -3362,25 +3559,25 @@
       <c r="B56" s="7">
         <v>46030</v>
       </c>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="20">
         <v>136158177</v>
       </c>
-      <c r="E56" s="22">
+      <c r="E56" s="20">
         <v>3450210478</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="G56" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H56" s="44" t="s">
+      <c r="H56" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I56" s="43">
+      <c r="I56" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3391,25 +3588,25 @@
       <c r="B57" s="7">
         <v>46030</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="20">
         <v>136159061</v>
       </c>
-      <c r="E57" s="22">
+      <c r="E57" s="20">
         <v>3450210522</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="G57" s="68" t="s">
+      <c r="G57" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H57" s="44" t="s">
+      <c r="H57" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I57" s="43">
+      <c r="I57" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3420,25 +3617,25 @@
       <c r="B58" s="7">
         <v>46030</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="20">
         <v>136159572</v>
       </c>
-      <c r="E58" s="22">
+      <c r="E58" s="20">
         <v>3450210555</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="68" t="s">
+      <c r="G58" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H58" s="44" t="s">
+      <c r="H58" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I58" s="43">
+      <c r="I58" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3449,25 +3646,25 @@
       <c r="B59" s="7">
         <v>46030</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="20">
         <v>136160934</v>
       </c>
-      <c r="E59" s="22">
+      <c r="E59" s="20">
         <v>3450210621</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G59" s="68" t="s">
+      <c r="G59" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H59" s="44" t="s">
+      <c r="H59" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I59" s="43">
+      <c r="I59" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3478,25 +3675,25 @@
       <c r="B60" s="7">
         <v>46030</v>
       </c>
-      <c r="C60" s="25" t="s">
+      <c r="C60" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="22">
+      <c r="D60" s="20">
         <v>136161602</v>
       </c>
-      <c r="E60" s="22">
+      <c r="E60" s="20">
         <v>3450210731</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G60" s="70" t="s">
+      <c r="G60" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="H60" s="44" t="s">
+      <c r="H60" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="I60" s="43">
+      <c r="I60" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3507,25 +3704,25 @@
       <c r="B61" s="7">
         <v>46030</v>
       </c>
-      <c r="C61" s="25" t="s">
+      <c r="C61" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="22">
+      <c r="D61" s="20">
         <v>136163135</v>
       </c>
-      <c r="E61" s="22">
+      <c r="E61" s="20">
         <v>3450210973</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G61" s="68" t="s">
+      <c r="G61" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H61" s="44" t="s">
+      <c r="H61" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="43">
+      <c r="I61" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3536,25 +3733,25 @@
       <c r="B62" s="7">
         <v>46030</v>
       </c>
-      <c r="C62" s="25" t="s">
+      <c r="C62" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D62" s="22">
+      <c r="D62" s="20">
         <v>136166168</v>
       </c>
-      <c r="E62" s="17">
+      <c r="E62" s="16">
         <v>3450211260</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="68" t="s">
+      <c r="G62" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H62" s="44" t="s">
+      <c r="H62" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I62" s="57">
+      <c r="I62" s="44">
         <v>46030</v>
       </c>
     </row>
@@ -3565,25 +3762,25 @@
       <c r="B63" s="7">
         <v>46030</v>
       </c>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="22">
+      <c r="D63" s="20">
         <v>136167576</v>
       </c>
-      <c r="E63" s="17">
+      <c r="E63" s="16">
         <v>3450211370</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="G63" s="68" t="s">
+      <c r="G63" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H63" s="44" t="s">
+      <c r="H63" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I63" s="43">
+      <c r="I63" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3594,25 +3791,25 @@
       <c r="B64" s="7">
         <v>46031</v>
       </c>
-      <c r="C64" s="25" t="s">
+      <c r="C64" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D64" s="22">
+      <c r="D64" s="20">
         <v>136170190</v>
       </c>
-      <c r="E64" s="17">
+      <c r="E64" s="16">
         <v>3450211480</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="G64" s="68" t="s">
+      <c r="G64" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="44" t="s">
+      <c r="H64" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I64" s="43">
+      <c r="I64" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3620,28 +3817,28 @@
       <c r="A65" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="46">
+      <c r="B65" s="33">
         <v>46030</v>
       </c>
-      <c r="C65" s="25" t="s">
+      <c r="C65" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="22">
+      <c r="D65" s="20">
         <v>136173186</v>
       </c>
-      <c r="E65" s="17">
+      <c r="E65" s="16">
         <v>3450210797</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="G65" s="68" t="s">
+      <c r="G65" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H65" s="44" t="s">
+      <c r="H65" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I65" s="43">
+      <c r="I65" s="30">
         <v>46030</v>
       </c>
     </row>
@@ -3652,25 +3849,25 @@
       <c r="B66" s="7">
         <v>46031</v>
       </c>
-      <c r="C66" s="25" t="s">
+      <c r="C66" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="22">
+      <c r="D66" s="20">
         <v>136177988</v>
       </c>
-      <c r="E66" s="17">
+      <c r="E66" s="16">
         <v>3450212282</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="G66" s="68" t="s">
+      <c r="G66" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H66" s="12" t="s">
+      <c r="H66" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I66" s="43">
+      <c r="I66" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3681,25 +3878,25 @@
       <c r="B67" s="7">
         <v>46031</v>
       </c>
-      <c r="C67" s="25" t="s">
+      <c r="C67" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="22">
+      <c r="D67" s="20">
         <v>136178449</v>
       </c>
-      <c r="E67" s="17">
+      <c r="E67" s="16">
         <v>3450212337</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="G67" s="68" t="s">
+      <c r="G67" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H67" s="12" t="s">
+      <c r="H67" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I67" s="43">
+      <c r="I67" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3710,25 +3907,25 @@
       <c r="B68" s="7">
         <v>46031</v>
       </c>
-      <c r="C68" s="25" t="s">
+      <c r="C68" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D68" s="22">
+      <c r="D68" s="20">
         <v>136178689</v>
       </c>
-      <c r="E68" s="17">
+      <c r="E68" s="16">
         <v>3450212370</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="G68" s="68" t="s">
+      <c r="G68" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H68" s="12" t="s">
+      <c r="H68" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I68" s="43">
+      <c r="I68" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3739,25 +3936,25 @@
       <c r="B69" s="7">
         <v>46031</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="22">
+      <c r="D69" s="20">
         <v>136181166</v>
       </c>
-      <c r="E69" s="17">
+      <c r="E69" s="16">
         <v>3450212634</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="G69" s="68" t="s">
+      <c r="G69" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H69" s="12" t="s">
+      <c r="H69" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I69" s="43">
+      <c r="I69" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3768,25 +3965,25 @@
       <c r="B70" s="7">
         <v>46031</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="20">
         <v>136186468</v>
       </c>
-      <c r="E70" s="17">
+      <c r="E70" s="16">
         <v>3450213151</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="G70" s="68" t="s">
+      <c r="G70" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="H70" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I70" s="43">
+      <c r="I70" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3797,25 +3994,25 @@
       <c r="B71" s="7">
         <v>46031</v>
       </c>
-      <c r="C71" s="25" t="s">
+      <c r="C71" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="20">
         <v>136187002</v>
       </c>
-      <c r="E71" s="17">
+      <c r="E71" s="16">
         <v>3450213228</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="G71" s="68" t="s">
+      <c r="G71" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H71" s="12" t="s">
+      <c r="H71" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I71" s="43">
+      <c r="I71" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3826,25 +4023,25 @@
       <c r="B72" s="7">
         <v>46031</v>
       </c>
-      <c r="C72" s="25" t="s">
+      <c r="C72" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="22">
+      <c r="D72" s="20">
         <v>136189995</v>
       </c>
-      <c r="E72" s="17">
+      <c r="E72" s="16">
         <v>3450213514</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="G72" s="68" t="s">
+      <c r="G72" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H72" s="12" t="s">
+      <c r="H72" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I72" s="43">
+      <c r="I72" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3855,25 +4052,25 @@
       <c r="B73" s="7">
         <v>46031</v>
       </c>
-      <c r="C73" s="25" t="s">
+      <c r="C73" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D73" s="20">
         <v>136190185</v>
       </c>
-      <c r="E73" s="17">
+      <c r="E73" s="16">
         <v>3450213525</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G73" s="68" t="s">
+      <c r="G73" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H73" s="12" t="s">
+      <c r="H73" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I73" s="43">
+      <c r="I73" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -3884,38 +4081,38 @@
       <c r="B74" s="7">
         <v>46031</v>
       </c>
-      <c r="C74" s="25" t="s">
+      <c r="C74" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="22">
+      <c r="D74" s="20">
         <v>136191230</v>
       </c>
-      <c r="E74" s="17">
+      <c r="E74" s="16">
         <v>3450213624</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G74" s="68" t="s">
+      <c r="G74" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I74" s="43">
+      <c r="I74" s="30">
         <v>46031</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="6"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="68"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="43"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="10"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="30"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -3943,69 +4140,69 @@
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="25.42578125" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" style="15" customWidth="1"/>
     <col min="5" max="5" width="29.85546875" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
     <col min="8" max="8" width="29.85546875" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="H1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="53">
+      <c r="A2" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="40">
         <v>46357</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="42">
         <v>3450214834</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="56" t="s">
+      <c r="G2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="44" t="s">
         <v>126</v>
       </c>
     </row>
@@ -4013,28 +4210,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="53">
+      <c r="B3" s="40">
         <v>46357</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="61">
+      <c r="E3" s="48">
         <v>3450189160</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="30" t="s">
         <v>126</v>
       </c>
     </row>
@@ -4045,25 +4242,25 @@
       <c r="B4" s="7">
         <v>46042</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>136138608</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <v>3450209147</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -4074,25 +4271,25 @@
       <c r="B5" s="7">
         <v>46034</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <v>136205150</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>3450214515</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -4103,25 +4300,25 @@
       <c r="B6" s="7">
         <v>46035</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <v>136236485</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <v>3450216760</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -4132,25 +4329,25 @@
       <c r="B7" s="7">
         <v>46036</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <v>136242492</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>3450217309</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -4161,25 +4358,25 @@
       <c r="B8" s="7">
         <v>46036</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <v>136237016</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="16">
         <v>3450216935</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -4190,25 +4387,25 @@
       <c r="B9" s="7">
         <v>46036</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <v>136237898</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>3450216968</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -4219,25 +4416,25 @@
       <c r="B10" s="7">
         <v>46036</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>136245655</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>3450217595</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -4248,25 +4445,25 @@
       <c r="B11" s="7">
         <v>46038</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="20">
         <v>136249313</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>3450217936</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="30">
         <v>46042</v>
       </c>
     </row>
@@ -4277,25 +4474,25 @@
       <c r="B12" s="7">
         <v>46036</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <v>136251637</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>3450218211</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -4306,25 +4503,25 @@
       <c r="B13" s="7">
         <v>46037</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>136258778</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>3450218541</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -4335,25 +4532,25 @@
       <c r="B14" s="7">
         <v>46034</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <v>136197660</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>3450213888</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -4364,25 +4561,25 @@
       <c r="B15" s="7">
         <v>46037</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <v>136263011</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="16">
         <v>3450218937</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G15" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -4393,25 +4590,25 @@
       <c r="B16" s="7">
         <v>46037</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <v>136256269</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>3450218409</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="G16" s="68" t="s">
+      <c r="G16" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -4422,25 +4619,25 @@
       <c r="B17" s="7">
         <v>46032</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <v>136192409</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="16">
         <v>3450213668</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="30">
         <v>46032</v>
       </c>
     </row>
@@ -4451,25 +4648,25 @@
       <c r="B18" s="7">
         <v>46036</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <v>136241303</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="16">
         <v>3450217155</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G18" s="68" t="s">
+      <c r="G18" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -4480,25 +4677,25 @@
       <c r="B19" s="7">
         <v>46038</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <v>136295931</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>3450221423</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -4509,25 +4706,25 @@
       <c r="B20" s="7">
         <v>46041</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <v>136310665</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="16">
         <v>3450222380</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="G20" s="68" t="s">
+      <c r="G20" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="30">
         <v>46041</v>
       </c>
     </row>
@@ -4538,25 +4735,25 @@
       <c r="B21" s="7">
         <v>46020</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <v>136078351</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="16">
         <v>3450200116</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="G21" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -4567,25 +4764,25 @@
       <c r="B22" s="7">
         <v>46029</v>
       </c>
-      <c r="C22" s="54" t="s">
+      <c r="C22" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <v>136142232</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="16">
         <v>3450209422</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="G22" s="68" t="s">
+      <c r="G22" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -4596,25 +4793,25 @@
       <c r="B23" s="7">
         <v>46029</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <v>136143250</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>3450209500</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="G23" s="68" t="s">
+      <c r="G23" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="30">
         <v>46042</v>
       </c>
     </row>
@@ -4625,25 +4822,25 @@
       <c r="B24" s="7">
         <v>46036</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="20">
         <v>136248476</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>3450217837</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="G24" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -4654,25 +4851,25 @@
       <c r="B25" s="7">
         <v>46038</v>
       </c>
-      <c r="C25" s="54" t="s">
+      <c r="C25" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="20">
         <v>136135971</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="16">
         <v>3450208641</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="G25" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -4683,25 +4880,25 @@
       <c r="B26" s="7">
         <v>46044</v>
       </c>
-      <c r="C26" s="54" t="s">
+      <c r="C26" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="20">
         <v>136137403</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="16">
         <v>3450208850</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="68" t="s">
+      <c r="G26" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="30">
         <v>46044</v>
       </c>
     </row>
@@ -4712,25 +4909,25 @@
       <c r="B27" s="7">
         <v>46040</v>
       </c>
-      <c r="C27" s="54" t="s">
+      <c r="C27" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="20">
         <v>136100653</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="16">
         <v>3450205484</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="G27" s="68" t="s">
+      <c r="G27" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -4741,25 +4938,25 @@
       <c r="B28" s="7">
         <v>46029</v>
       </c>
-      <c r="C28" s="54" t="s">
+      <c r="C28" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="20">
         <v>136131576</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="16">
         <v>3450208256</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="G28" s="68" t="s">
+      <c r="G28" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -4770,25 +4967,25 @@
       <c r="B29" s="7">
         <v>46052</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="20">
         <v>136134008</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="16">
         <v>3450208410</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="G29" s="68" t="s">
+      <c r="G29" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -4799,25 +4996,25 @@
       <c r="B30" s="7">
         <v>46044</v>
       </c>
-      <c r="C30" s="54" t="s">
+      <c r="C30" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="20">
         <v>136245494</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="16">
         <v>3450217584</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="68" t="s">
+      <c r="G30" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="30">
         <v>46042</v>
       </c>
     </row>
@@ -4828,25 +5025,25 @@
       <c r="B31" s="7">
         <v>46029</v>
       </c>
-      <c r="C31" s="54" t="s">
+      <c r="C31" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="20">
         <v>136143609</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>3450209543</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="G31" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -4857,25 +5054,25 @@
       <c r="B32" s="7">
         <v>46054</v>
       </c>
-      <c r="C32" s="54" t="s">
+      <c r="C32" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="20">
         <v>136204550</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>3450214460</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="G32" s="68" t="s">
+      <c r="G32" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -4886,25 +5083,25 @@
       <c r="B33" s="7">
         <v>46034</v>
       </c>
-      <c r="C33" s="54" t="s">
+      <c r="C33" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="20">
         <v>136206999</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="16">
         <v>3450214669</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="G33" s="68" t="s">
+      <c r="G33" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="30">
         <v>46034</v>
       </c>
     </row>
@@ -4915,49 +5112,49 @@
       <c r="B34" s="7">
         <v>46037</v>
       </c>
-      <c r="C34" s="54" t="s">
+      <c r="C34" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="20">
         <v>136283913</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="16">
         <v>3450219740</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G34" s="68" t="s">
+      <c r="G34" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="30">
         <v>46037</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="43"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="43"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="30"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -4983,14 +5180,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25" style="16" customWidth="1"/>
+    <col min="2" max="2" width="25" style="15" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="30.5703125" style="15" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="24" customWidth="1"/>
+    <col min="9" max="9" width="21" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5018,7 +5215,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5026,28 +5223,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="59">
+      <c r="B2" s="46">
         <v>46030</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="23">
         <v>46043</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="20">
         <v>136168042</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="16">
         <v>3450211435</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -5055,28 +5252,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="59">
+      <c r="B3" s="46">
         <v>46036</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="23">
         <v>46043</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="20">
         <v>136235650</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="16">
         <v>3450216858</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -5084,28 +5281,28 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="46">
         <v>46040</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="23">
         <v>46043</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>136240866</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <v>3450217111</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="30">
         <v>46042</v>
       </c>
     </row>
@@ -5113,28 +5310,28 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="59">
+      <c r="B5" s="46">
         <v>46037</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="23">
         <v>46043</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <v>136259760</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>3450218629</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="G5" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="34">
         <v>46037</v>
       </c>
     </row>
@@ -5142,28 +5339,28 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="59">
+      <c r="B6" s="46">
         <v>46037</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="23">
         <v>46043</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <v>136272873</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <v>3450219916</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5171,28 +5368,28 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="59">
+      <c r="B7" s="46">
         <v>46037</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="23">
         <v>46043</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <v>136267964</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>3450219400</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="30">
         <v>46042</v>
       </c>
     </row>
@@ -5200,28 +5397,28 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="59">
+      <c r="B8" s="46">
         <v>46036</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="23">
         <v>46043</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <v>136247223</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="16">
         <v>3450217750</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -5229,28 +5426,28 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="59">
+      <c r="B9" s="46">
         <v>46037</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="23">
         <v>46043</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <v>136285232</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>3450219619</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5258,28 +5455,28 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="59">
+      <c r="B10" s="46">
         <v>46042</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="23">
         <v>46043</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>136328294</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>3450223590</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="30">
         <v>46043</v>
       </c>
     </row>
@@ -5287,28 +5484,28 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="59">
+      <c r="B11" s="46">
         <v>46034</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <v>46043</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="20">
         <v>136204484</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>3450214449</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="30">
         <v>46041</v>
       </c>
     </row>
@@ -5316,28 +5513,28 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="59">
+      <c r="B12" s="46">
         <v>46037</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="23">
         <v>46043</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <v>136261498</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>3450218740</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5345,28 +5542,28 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="59">
+      <c r="B13" s="46">
         <v>46030</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="23">
         <v>46043</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>136155031</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>3450210005</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5374,28 +5571,28 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="59">
+      <c r="B14" s="46">
         <v>46037</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="23">
         <v>46043</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <v>136268608</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>3450219509</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="G14" s="72" t="s">
+      <c r="G14" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5403,28 +5600,28 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="59">
+      <c r="B15" s="46">
         <v>46030</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="23">
         <v>46043</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <v>136161590</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="16">
         <v>3450210720</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G15" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5432,28 +5629,28 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="59">
+      <c r="B16" s="46">
         <v>46037</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="23">
         <v>46043</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <v>136263581</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>3450219025</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="G16" s="68" t="s">
+      <c r="G16" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5464,25 +5661,25 @@
       <c r="B17" s="7">
         <v>46032</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="23">
         <v>46043</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <v>136156332</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="16">
         <v>3450210280</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5493,25 +5690,25 @@
       <c r="B18" s="7">
         <v>46036</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="23">
         <v>46043</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <v>136237446</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="16">
         <v>3450216946</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="G18" s="68" t="s">
+      <c r="G18" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -5522,25 +5719,25 @@
       <c r="B19" s="7">
         <v>46036</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="23">
         <v>46043</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <v>136250722</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>3450218080</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -5551,25 +5748,25 @@
       <c r="B20" s="7">
         <v>46041</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="23">
         <v>46043</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <v>136343395</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="16">
         <v>3450221698</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="30">
         <v>46041</v>
       </c>
     </row>
@@ -5580,25 +5777,25 @@
       <c r="B21" s="7">
         <v>46037</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="23">
         <v>46043</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <v>136267310</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="16">
         <v>3450219366</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="G21" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="I21" s="47">
+      <c r="I21" s="34">
         <v>46037</v>
       </c>
     </row>
@@ -5609,25 +5806,25 @@
       <c r="B22" s="7">
         <v>46030</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="23">
         <v>46043</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <v>136157001</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="16">
         <v>3450210335</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="G22" s="65" t="s">
+      <c r="G22" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="30">
         <v>46042</v>
       </c>
     </row>
@@ -5638,25 +5835,25 @@
       <c r="B23" s="7">
         <v>46035</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="23">
         <v>46043</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <v>136241493</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>3450215450</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="73" t="s">
+      <c r="H23" s="60" t="s">
         <v>219</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -5667,38 +5864,38 @@
       <c r="B24" s="7">
         <v>46035</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="23">
         <v>46043</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="20">
         <v>136239432</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>3450215934</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="73" t="s">
+      <c r="H24" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="30">
         <v>46035</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="43"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="30"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -5771,28 +5968,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="63" t="s">
         <v>224</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="12">
         <v>3450218431</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="G2" s="74" t="s">
+      <c r="G2" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="30" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5800,28 +5997,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="23">
         <v>46037</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D3" s="78">
+      <c r="D3" s="20">
         <v>136259803</v>
       </c>
-      <c r="E3" s="76">
+      <c r="E3" s="62">
         <v>3450218630</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="G3" s="74" t="s">
+      <c r="G3" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="30">
         <v>46043</v>
       </c>
     </row>
@@ -5829,28 +6026,28 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="23">
         <v>46037</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D4" s="78">
+      <c r="D4" s="20">
         <v>136265038</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="62">
         <v>3450219179</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="G4" s="74" t="s">
+      <c r="G4" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5861,25 +6058,25 @@
       <c r="B5" s="7">
         <v>46037</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D5" s="78">
+      <c r="D5" s="20">
         <v>136268873</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="62">
         <v>3450219520</v>
       </c>
-      <c r="F5" s="75" t="s">
+      <c r="F5" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5890,25 +6087,25 @@
       <c r="B6" s="7">
         <v>46042</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="20">
         <v>136323633</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="62">
         <v>3450223150</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="30">
         <v>46042</v>
       </c>
     </row>
@@ -5919,25 +6116,25 @@
       <c r="B7" s="7">
         <v>46043</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="78">
+      <c r="D7" s="20">
         <v>136346545</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="62">
         <v>3450224680</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="30">
         <v>46043</v>
       </c>
     </row>
@@ -5948,25 +6145,25 @@
       <c r="B8" s="7">
         <v>46037</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="78">
+      <c r="D8" s="20">
         <v>136283841</v>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="62">
         <v>3450218717</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="30">
         <v>46037</v>
       </c>
     </row>
@@ -5977,25 +6174,25 @@
       <c r="B9" s="7">
         <v>46031</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D9" s="78">
+      <c r="D9" s="20">
         <v>136189133</v>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="62">
         <v>3450213459</v>
       </c>
-      <c r="F9" s="75" t="s">
+      <c r="F9" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="H9" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -6006,25 +6203,25 @@
       <c r="B10" s="7">
         <v>46031</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D10" s="78">
+      <c r="D10" s="20">
         <v>136190909</v>
       </c>
-      <c r="E10" s="76">
+      <c r="E10" s="62">
         <v>3450213569</v>
       </c>
-      <c r="F10" s="75" t="s">
+      <c r="F10" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="G10" s="74" t="s">
+      <c r="G10" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="80" t="s">
+      <c r="H10" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="30">
         <v>46031</v>
       </c>
     </row>
@@ -6035,25 +6232,25 @@
       <c r="B11" s="7">
         <v>46038</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="78">
+      <c r="D11" s="20">
         <v>136284770</v>
       </c>
-      <c r="E11" s="76">
+      <c r="E11" s="62">
         <v>3450220576</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -6064,25 +6261,25 @@
       <c r="B12" s="7">
         <v>46049</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D12" s="78">
+      <c r="D12" s="20">
         <v>136187231</v>
       </c>
-      <c r="E12" s="76">
+      <c r="E12" s="62">
         <v>3450213283</v>
       </c>
-      <c r="F12" s="75" t="s">
+      <c r="F12" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="G12" s="74" t="s">
+      <c r="G12" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="80" t="s">
+      <c r="H12" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="30">
         <v>46035</v>
       </c>
     </row>
@@ -6093,25 +6290,25 @@
       <c r="B13" s="7">
         <v>46055</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D13" s="78">
+      <c r="D13" s="20">
         <v>136279831</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="62">
         <v>3450217210</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="30">
         <v>46043</v>
       </c>
     </row>
@@ -6122,25 +6319,25 @@
       <c r="B14" s="7">
         <v>46037</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="78">
+      <c r="D14" s="20">
         <v>136258212</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="62">
         <v>3450218520</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="G14" s="74" t="s">
+      <c r="G14" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="30">
         <v>46043</v>
       </c>
     </row>
@@ -6151,25 +6348,25 @@
       <c r="B15" s="7">
         <v>46031</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="78">
+      <c r="D15" s="20">
         <v>136180926</v>
       </c>
-      <c r="E15" s="76">
+      <c r="E15" s="62">
         <v>3450212612</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="80" t="s">
+      <c r="H15" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -6180,25 +6377,25 @@
       <c r="B16" s="7">
         <v>46038</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D16" s="78">
+      <c r="D16" s="20">
         <v>136276674</v>
       </c>
-      <c r="E16" s="76">
+      <c r="E16" s="62">
         <v>3450220004</v>
       </c>
-      <c r="F16" s="75" t="s">
+      <c r="F16" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="30">
         <v>46038</v>
       </c>
     </row>
@@ -6209,25 +6406,25 @@
       <c r="B17" s="7">
         <v>46036</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D17" s="78">
+      <c r="D17" s="20">
         <v>136261227</v>
       </c>
-      <c r="E17" s="76">
+      <c r="E17" s="62">
         <v>3450216979</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="30">
         <v>46036</v>
       </c>
     </row>
@@ -6235,23 +6432,23 @@
       <c r="A18" s="6"/>
       <c r="B18" s="8"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="43"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="30"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="79"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="64"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -6259,10 +6456,10 @@
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -6272,8 +6469,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="12"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -6283,8 +6480,8 @@
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="12"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -6294,8 +6491,8 @@
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="12"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -6305,8 +6502,8 @@
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="12"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -6316,8 +6513,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="12"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -6327,8 +6524,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="12"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -6338,8 +6535,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="12"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -6349,8 +6546,8 @@
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="12"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -6360,8 +6557,8 @@
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="12"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -6371,8 +6568,8 @@
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="12"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -6394,16 +6591,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6414,25 +6612,25 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="67" t="s">
         <v>8</v>
       </c>
     </row>
@@ -6440,545 +6638,923 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="B2" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D2" s="71">
+        <v>136201349</v>
+      </c>
+      <c r="E2" s="16">
+        <v>3450214207</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="68">
+        <v>46034</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="32"/>
+      <c r="B3" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C3" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D3" s="71">
+        <v>136204083</v>
+      </c>
+      <c r="E3" s="16">
+        <v>3450214416</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="69">
+        <v>46034</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="B4" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C4" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D4" s="71">
+        <v>136210420</v>
+      </c>
+      <c r="E4" s="16">
+        <v>3450215054</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="68">
+        <v>46034</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="B5" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C5" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D5" s="71">
+        <v>136217497</v>
+      </c>
+      <c r="E5" s="16">
+        <v>3450215439</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="68">
+        <v>46035</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C6" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D6" s="71">
+        <v>136222466</v>
+      </c>
+      <c r="E6" s="16">
+        <v>3450215967</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="68">
+        <v>46035</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C7" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D7" s="71">
+        <v>136229051</v>
+      </c>
+      <c r="E7" s="16">
+        <v>3450216528</v>
+      </c>
+      <c r="F7" s="65" t="s">
+        <v>254</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="68">
+        <v>46035</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>46039</v>
+      </c>
+      <c r="C8" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D8" s="71">
+        <v>136298386</v>
+      </c>
+      <c r="E8" s="16">
+        <v>3450221445</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="I8" s="68">
+        <v>46039</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>46043</v>
+      </c>
+      <c r="C9" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D9" s="71">
+        <v>136308843</v>
+      </c>
+      <c r="E9" s="16">
+        <v>3450222237</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>257</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="79" t="s">
+        <v>258</v>
+      </c>
+      <c r="I9" s="68">
+        <v>46043</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C10" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D10" s="71">
+        <v>136331715</v>
+      </c>
+      <c r="E10" s="16">
+        <v>3450223799</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>259</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="I10" s="68">
+        <v>46044</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C11" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D11" s="71">
+        <v>136347242</v>
+      </c>
+      <c r="E11" s="16">
+        <v>3450223106</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="68">
+        <v>46042</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C12" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D12" s="71">
+        <v>136364491</v>
+      </c>
+      <c r="E12" s="16">
+        <v>3450226109</v>
+      </c>
+      <c r="F12" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="68">
+        <v>46044</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D13" s="71">
+        <v>136370351</v>
+      </c>
+      <c r="E13" s="16">
+        <v>3450226615</v>
+      </c>
+      <c r="F13" s="65" t="s">
+        <v>263</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="68">
+        <v>46044</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
+      <c r="A14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7">
+        <v>46039</v>
+      </c>
+      <c r="C14" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D14" s="71">
+        <v>136172680</v>
+      </c>
+      <c r="E14" s="16">
+        <v>3450211699</v>
+      </c>
+      <c r="F14" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="79" t="s">
+        <v>209</v>
+      </c>
+      <c r="I14" s="68">
+        <v>46037</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C15" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D15" s="71">
+        <v>136195579</v>
+      </c>
+      <c r="E15" s="16">
+        <v>3450213558</v>
+      </c>
+      <c r="F15" s="65" t="s">
+        <v>265</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="68">
+        <v>46031</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C16" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D16" s="71">
+        <v>136197359</v>
+      </c>
+      <c r="E16" s="16">
+        <v>3450211820</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="68">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C17" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D17" s="71">
+        <v>136197589</v>
+      </c>
+      <c r="E17" s="16">
+        <v>3450211886</v>
+      </c>
+      <c r="F17" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="68">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C18" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D18" s="71">
+        <v>136197799</v>
+      </c>
+      <c r="E18" s="16">
+        <v>3450213899</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>268</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="68">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C19" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D19" s="71">
+        <v>136199140</v>
+      </c>
+      <c r="E19" s="16">
+        <v>3450212470</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="68">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C20" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D20" s="71">
+        <v>136204512</v>
+      </c>
+      <c r="E20" s="16">
+        <v>3450214450</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="68">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C21" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D21" s="71">
+        <v>136205901</v>
+      </c>
+      <c r="E21" s="16">
+        <v>3450214570</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>271</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="68">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C22" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D22" s="71">
+        <v>136209337</v>
+      </c>
+      <c r="E22" s="16">
+        <v>3450214890</v>
+      </c>
+      <c r="F22" s="65" t="s">
+        <v>272</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="68">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C23" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D23" s="71">
+        <v>136212010</v>
+      </c>
+      <c r="E23" s="16">
+        <v>3450215175</v>
+      </c>
+      <c r="F23" s="65" t="s">
+        <v>273</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="68">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C24" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D24" s="71">
+        <v>136212633</v>
+      </c>
+      <c r="E24" s="16">
+        <v>3450215208</v>
+      </c>
+      <c r="F24" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="68">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C25" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D25" s="71">
+        <v>136251023</v>
+      </c>
+      <c r="E25" s="16">
+        <v>3450218134</v>
+      </c>
+      <c r="F25" s="65" t="s">
+        <v>275</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="I25" s="68">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C26" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D26" s="71">
+        <v>136273446</v>
+      </c>
+      <c r="E26" s="16">
+        <v>3450219960</v>
+      </c>
+      <c r="F26" s="65" t="s">
+        <v>277</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="68">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C27" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D27" s="71">
+        <v>136220882</v>
+      </c>
+      <c r="E27" s="16">
+        <v>3450215725</v>
+      </c>
+      <c r="F27" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="68">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C28" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D28" s="71">
+        <v>136222733</v>
+      </c>
+      <c r="E28" s="16">
+        <v>3450215978</v>
+      </c>
+      <c r="F28" s="65" t="s">
+        <v>279</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" s="68">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C29" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D29" s="71">
+        <v>136222970</v>
+      </c>
+      <c r="E29" s="16">
+        <v>3450215989</v>
+      </c>
+      <c r="F29" s="65" t="s">
+        <v>280</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I29" s="68">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C30" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D30" s="71">
+        <v>136227006</v>
+      </c>
+      <c r="E30" s="16">
+        <v>3450216319</v>
+      </c>
+      <c r="F30" s="65" t="s">
+        <v>281</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" s="68">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C31" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D31" s="71">
+        <v>136231067</v>
+      </c>
+      <c r="E31" s="16">
+        <v>3450216715</v>
+      </c>
+      <c r="F31" s="65" t="s">
+        <v>282</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="79" t="s">
+        <v>283</v>
+      </c>
+      <c r="I31" s="68">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C32" s="23">
+        <v>46045</v>
+      </c>
+      <c r="D32" s="71">
+        <v>136232394</v>
+      </c>
+      <c r="E32" s="16">
+        <v>3450216836</v>
+      </c>
+      <c r="F32" s="65" t="s">
+        <v>284</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="68">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="70"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6988,688 +7564,517 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="24"/>
+      <c r="A2" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="30">
+        <v>46038</v>
+      </c>
+      <c r="C2" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D2" s="71">
+        <v>136196463</v>
+      </c>
+      <c r="E2" s="16">
+        <v>3450213790</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>285</v>
+      </c>
+      <c r="G2" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="77" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="24"/>
+      <c r="A3" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="30">
+        <v>46036</v>
+      </c>
+      <c r="C3" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D3" s="71">
+        <v>136248629</v>
+      </c>
+      <c r="E3" s="16">
+        <v>3450217859</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>287</v>
+      </c>
+      <c r="G3" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="24"/>
+      <c r="A4" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="30">
+        <v>46036</v>
+      </c>
+      <c r="C4" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D4" s="71">
+        <v>136250076</v>
+      </c>
+      <c r="E4" s="16">
+        <v>3450218013</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="G4" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="24"/>
+      <c r="A5" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="30">
+        <v>46058</v>
+      </c>
+      <c r="C5" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D5" s="71">
+        <v>136247155</v>
+      </c>
+      <c r="E5" s="16">
+        <v>3450217738</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="77" t="s">
+        <v>290</v>
+      </c>
+      <c r="I5" s="30">
+        <v>46042</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="24"/>
+      <c r="A6" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="30">
+        <v>46036</v>
+      </c>
+      <c r="C6" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D6" s="71">
+        <v>136252158</v>
+      </c>
+      <c r="E6" s="16">
+        <v>3450218255</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>291</v>
+      </c>
+      <c r="G6" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="24"/>
+      <c r="A7" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="30">
+        <v>46034</v>
+      </c>
+      <c r="C7" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D7" s="71">
+        <v>136200431</v>
+      </c>
+      <c r="E7" s="16">
+        <v>3450214075</v>
+      </c>
+      <c r="F7" s="65" t="s">
+        <v>292</v>
+      </c>
+      <c r="G7" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="78" t="s">
+        <v>293</v>
+      </c>
+      <c r="I7" s="30">
+        <v>46041</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="24"/>
+      <c r="A8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="30">
+        <v>46063</v>
+      </c>
+      <c r="C8" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D8" s="71">
+        <v>136221889</v>
+      </c>
+      <c r="E8" s="16">
+        <v>3450215846</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>294</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="78" t="s">
+        <v>295</v>
+      </c>
+      <c r="I8" s="30">
+        <v>46038</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="24"/>
+      <c r="A9" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="30">
+        <v>46035</v>
+      </c>
+      <c r="C9" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D9" s="71">
+        <v>136237144</v>
+      </c>
+      <c r="E9" s="16">
+        <v>3450216451</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="G9" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="30">
+        <v>46035</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="24"/>
+      <c r="A10" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="30">
+        <v>46035</v>
+      </c>
+      <c r="C10" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D10" s="71">
+        <v>136237408</v>
+      </c>
+      <c r="E10" s="16">
+        <v>3450216430</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="G10" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="30">
+        <v>46035</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="24"/>
+      <c r="A11" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="30">
+        <v>46035</v>
+      </c>
+      <c r="C11" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D11" s="71">
+        <v>136239635</v>
+      </c>
+      <c r="E11" s="16">
+        <v>3450215890</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>298</v>
+      </c>
+      <c r="G11" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="30">
+        <v>46035</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="24"/>
+      <c r="A12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="30">
+        <v>46036</v>
+      </c>
+      <c r="C12" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D12" s="71">
+        <v>136240177</v>
+      </c>
+      <c r="E12" s="16">
+        <v>3450217078</v>
+      </c>
+      <c r="F12" s="65" t="s">
+        <v>299</v>
+      </c>
+      <c r="G12" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="24"/>
+      <c r="A13" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="30">
+        <v>46036</v>
+      </c>
+      <c r="C13" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D13" s="71">
+        <v>136241410</v>
+      </c>
+      <c r="E13" s="16">
+        <v>3450217166</v>
+      </c>
+      <c r="F13" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="G13" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="24"/>
+      <c r="A14" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="30">
+        <v>46036</v>
+      </c>
+      <c r="C14" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D14" s="71">
+        <v>136248577</v>
+      </c>
+      <c r="E14" s="16">
+        <v>3450217848</v>
+      </c>
+      <c r="F14" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="G14" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="24"/>
+      <c r="A15" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="30">
+        <v>46036</v>
+      </c>
+      <c r="C15" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D15" s="71">
+        <v>136249013</v>
+      </c>
+      <c r="E15" s="16">
+        <v>3450217903</v>
+      </c>
+      <c r="F15" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="G15" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="30">
+        <v>46036</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="24"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
+      <c r="A16" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="30">
+        <v>46039</v>
+      </c>
+      <c r="C16" s="30">
+        <v>46046</v>
+      </c>
+      <c r="D16" s="71">
+        <v>136249524</v>
+      </c>
+      <c r="E16" s="16">
+        <v>3450217969</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="G16" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="I16" s="30">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="28"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="24"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="30"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="24"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="24"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="24"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="24"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="24"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="24"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="24"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="24"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="24"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="24"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="24"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="24"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="24"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-      <c r="I37"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="I39"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-      <c r="I40"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-      <c r="I41"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-      <c r="I42"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-      <c r="I43"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-      <c r="I44"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-      <c r="I45"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="30"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G18" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7679,7 +8084,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E6B8A0-66E5-406F-8D37-9E8A2778B9CB}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -7727,496 +8132,353 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="43"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="30"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="43"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="43"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="43"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="30"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="43"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="30"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="43"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="30"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="43"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="30"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="43"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="43"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="30"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="43"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="30"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="43"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="30"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="43"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="30"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="43"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="43"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="30"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="43"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="30"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="24" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="43"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="30"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="43"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="30"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="43"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="30"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="43"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="30"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="43"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="30"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="43"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="30"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="43"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="30"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="43"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="30"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="43"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="30"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="43"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="30"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="43"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="30"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="43"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="30"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="43"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="30"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="43"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="43"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="43"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="43"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="43"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="43"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="43"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="43"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="43"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="43"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="43"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="43"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="43"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="30"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -8225,10 +8487,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19:A42" xr:uid="{EC7C7A5C-617A-4EC2-BB80-7CA761AA8730}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19:A30" xr:uid="{EC7C7A5C-617A-4EC2-BB80-7CA761AA8730}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G43" xr:uid="{C8229196-52D6-4347-81FE-B1256BABDAAC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G30" xr:uid="{C8229196-52D6-4347-81FE-B1256BABDAAC}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8249,58 +8511,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540083</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540083</Url>
-      <Description>QAFFA7D2F2TC-2102087286-540083</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="06364c42bcbf61016b6bd5e32d4d0782">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="199c6c2eefa6ec2f672a95412cfea747" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8684,6 +8894,58 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540083</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540083</Url>
+      <Description>QAFFA7D2F2TC-2102087286-540083</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
@@ -8735,7 +8997,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EB5007-F016-4E17-BC8B-56A069F0892C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8743,7 +9005,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EB5007-F016-4E17-BC8B-56A069F0892C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
